--- a/seperation_tests.xlsx
+++ b/seperation_tests.xlsx
@@ -521,7 +521,11 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Puits_51</t>
+        </is>
+      </c>
       <c r="C2" s="1" t="n">
         <v>45265</v>
       </c>
@@ -584,7 +588,11 @@
       <c r="A3" t="n">
         <v>1</v>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Puits_51</t>
+        </is>
+      </c>
       <c r="C3" s="1" t="n">
         <v>45265</v>
       </c>
@@ -647,7 +655,11 @@
       <c r="A4" t="n">
         <v>1</v>
       </c>
-      <c r="B4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Puits_51</t>
+        </is>
+      </c>
       <c r="C4" s="1" t="n">
         <v>45265</v>
       </c>
@@ -710,7 +722,11 @@
       <c r="A5" t="n">
         <v>2</v>
       </c>
-      <c r="B5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Puits_140</t>
+        </is>
+      </c>
       <c r="C5" s="1" t="n">
         <v>45271</v>
       </c>
@@ -771,7 +787,11 @@
       <c r="A6" t="n">
         <v>2</v>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Puits_140</t>
+        </is>
+      </c>
       <c r="C6" s="1" t="n">
         <v>45271</v>
       </c>
@@ -832,7 +852,11 @@
       <c r="A7" t="n">
         <v>2</v>
       </c>
-      <c r="B7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Puits_140</t>
+        </is>
+      </c>
       <c r="C7" s="1" t="n">
         <v>45271</v>
       </c>
@@ -893,7 +917,11 @@
       <c r="A8" t="n">
         <v>3</v>
       </c>
-      <c r="B8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Puits_49</t>
+        </is>
+      </c>
       <c r="C8" s="1" t="n">
         <v>45317</v>
       </c>
@@ -958,7 +986,11 @@
       <c r="A9" t="n">
         <v>3</v>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Puits_49</t>
+        </is>
+      </c>
       <c r="C9" s="1" t="n">
         <v>45318</v>
       </c>
@@ -1021,7 +1053,11 @@
       <c r="A10" t="n">
         <v>3</v>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Puits_49</t>
+        </is>
+      </c>
       <c r="C10" s="1" t="n">
         <v>45318</v>
       </c>
@@ -1086,7 +1122,11 @@
       <c r="A11" t="n">
         <v>4</v>
       </c>
-      <c r="B11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Puits_215</t>
+        </is>
+      </c>
       <c r="C11" s="1" t="n">
         <v>45320</v>
       </c>
@@ -1149,7 +1189,11 @@
       <c r="A12" t="n">
         <v>4</v>
       </c>
-      <c r="B12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Puits_215</t>
+        </is>
+      </c>
       <c r="C12" s="1" t="n">
         <v>45321</v>
       </c>
@@ -1212,7 +1256,11 @@
       <c r="A13" t="n">
         <v>4</v>
       </c>
-      <c r="B13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Puits_215</t>
+        </is>
+      </c>
       <c r="C13" s="1" t="n">
         <v>45321</v>
       </c>
@@ -1275,7 +1323,11 @@
       <c r="A14" t="n">
         <v>5</v>
       </c>
-      <c r="B14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Puits_101</t>
+        </is>
+      </c>
       <c r="C14" s="1" t="n">
         <v>45322</v>
       </c>
@@ -1338,7 +1390,11 @@
       <c r="A15" t="n">
         <v>5</v>
       </c>
-      <c r="B15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Puits_101</t>
+        </is>
+      </c>
       <c r="C15" s="1" t="n">
         <v>45323</v>
       </c>
@@ -1401,7 +1457,11 @@
       <c r="A16" t="n">
         <v>5</v>
       </c>
-      <c r="B16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Puits_101</t>
+        </is>
+      </c>
       <c r="C16" s="1" t="n">
         <v>45323</v>
       </c>
@@ -1464,7 +1524,11 @@
       <c r="A17" t="n">
         <v>6</v>
       </c>
-      <c r="B17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Puits_87</t>
+        </is>
+      </c>
       <c r="C17" s="1" t="n">
         <v>45325</v>
       </c>
@@ -1527,7 +1591,11 @@
       <c r="A18" t="n">
         <v>6</v>
       </c>
-      <c r="B18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Puits_87</t>
+        </is>
+      </c>
       <c r="C18" s="1" t="n">
         <v>45325</v>
       </c>
@@ -1590,7 +1658,11 @@
       <c r="A19" t="n">
         <v>6</v>
       </c>
-      <c r="B19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Puits_87</t>
+        </is>
+      </c>
       <c r="C19" s="1" t="n">
         <v>45326</v>
       </c>
@@ -1653,7 +1725,11 @@
       <c r="A20" t="n">
         <v>7</v>
       </c>
-      <c r="B20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Puits_99</t>
+        </is>
+      </c>
       <c r="C20" s="1" t="n">
         <v>45327</v>
       </c>
@@ -1716,7 +1792,11 @@
       <c r="A21" t="n">
         <v>7</v>
       </c>
-      <c r="B21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Puits_99</t>
+        </is>
+      </c>
       <c r="C21" s="1" t="n">
         <v>45328</v>
       </c>
@@ -1779,7 +1859,11 @@
       <c r="A22" t="n">
         <v>7</v>
       </c>
-      <c r="B22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Puits_99</t>
+        </is>
+      </c>
       <c r="C22" s="1" t="n">
         <v>45328</v>
       </c>
@@ -1842,7 +1926,11 @@
       <c r="A23" t="n">
         <v>8</v>
       </c>
-      <c r="B23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Puits_218</t>
+        </is>
+      </c>
       <c r="C23" s="1" t="n">
         <v>45330</v>
       </c>
@@ -1905,7 +1993,11 @@
       <c r="A24" t="n">
         <v>8</v>
       </c>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Puits_218</t>
+        </is>
+      </c>
       <c r="C24" s="1" t="n">
         <v>45330</v>
       </c>
@@ -1968,7 +2060,11 @@
       <c r="A25" t="n">
         <v>8</v>
       </c>
-      <c r="B25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Puits_218</t>
+        </is>
+      </c>
       <c r="C25" s="1" t="n">
         <v>45331</v>
       </c>
@@ -2031,7 +2127,11 @@
       <c r="A26" t="n">
         <v>9</v>
       </c>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Puits_216</t>
+        </is>
+      </c>
       <c r="C26" s="1" t="n">
         <v>45332</v>
       </c>
@@ -2094,7 +2194,11 @@
       <c r="A27" t="n">
         <v>9</v>
       </c>
-      <c r="B27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Puits_216</t>
+        </is>
+      </c>
       <c r="C27" s="1" t="n">
         <v>45333</v>
       </c>
@@ -2157,7 +2261,11 @@
       <c r="A28" t="n">
         <v>9</v>
       </c>
-      <c r="B28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Puits_216</t>
+        </is>
+      </c>
       <c r="C28" s="1" t="n">
         <v>45333</v>
       </c>
@@ -2220,7 +2328,11 @@
       <c r="A29" t="n">
         <v>10</v>
       </c>
-      <c r="B29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Puits_214</t>
+        </is>
+      </c>
       <c r="C29" s="1" t="n">
         <v>45334</v>
       </c>
@@ -2283,7 +2395,11 @@
       <c r="A30" t="n">
         <v>10</v>
       </c>
-      <c r="B30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Puits_214</t>
+        </is>
+      </c>
       <c r="C30" s="1" t="n">
         <v>45335</v>
       </c>
@@ -2346,7 +2462,11 @@
       <c r="A31" t="n">
         <v>10</v>
       </c>
-      <c r="B31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Puits_214</t>
+        </is>
+      </c>
       <c r="C31" s="1" t="n">
         <v>45335</v>
       </c>
@@ -2409,7 +2529,11 @@
       <c r="A32" t="n">
         <v>11</v>
       </c>
-      <c r="B32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Puits_200</t>
+        </is>
+      </c>
       <c r="C32" s="1" t="n">
         <v>45336</v>
       </c>
@@ -2472,7 +2596,11 @@
       <c r="A33" t="n">
         <v>11</v>
       </c>
-      <c r="B33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Puits_200</t>
+        </is>
+      </c>
       <c r="C33" s="1" t="n">
         <v>45337</v>
       </c>
@@ -2535,7 +2663,11 @@
       <c r="A34" t="n">
         <v>11</v>
       </c>
-      <c r="B34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Puits_200</t>
+        </is>
+      </c>
       <c r="C34" s="1" t="n">
         <v>45337</v>
       </c>
@@ -2598,7 +2730,11 @@
       <c r="A35" t="n">
         <v>12</v>
       </c>
-      <c r="B35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Puits_208</t>
+        </is>
+      </c>
       <c r="C35" s="1" t="n">
         <v>45338</v>
       </c>
@@ -2661,7 +2797,11 @@
       <c r="A36" t="n">
         <v>12</v>
       </c>
-      <c r="B36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Puits_208</t>
+        </is>
+      </c>
       <c r="C36" s="1" t="n">
         <v>45339</v>
       </c>
@@ -2724,7 +2864,11 @@
       <c r="A37" t="n">
         <v>12</v>
       </c>
-      <c r="B37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Puits_208</t>
+        </is>
+      </c>
       <c r="C37" s="1" t="n">
         <v>45339</v>
       </c>
@@ -2787,7 +2931,11 @@
       <c r="A38" t="n">
         <v>13</v>
       </c>
-      <c r="B38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Puits_42</t>
+        </is>
+      </c>
       <c r="C38" s="1" t="n">
         <v>45340</v>
       </c>
@@ -2850,7 +2998,11 @@
       <c r="A39" t="n">
         <v>13</v>
       </c>
-      <c r="B39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Puits_42</t>
+        </is>
+      </c>
       <c r="C39" s="1" t="n">
         <v>45341</v>
       </c>
@@ -2913,7 +3065,11 @@
       <c r="A40" t="n">
         <v>13</v>
       </c>
-      <c r="B40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Puits_42</t>
+        </is>
+      </c>
       <c r="C40" s="1" t="n">
         <v>45341</v>
       </c>
@@ -2976,7 +3132,11 @@
       <c r="A41" t="n">
         <v>14</v>
       </c>
-      <c r="B41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Puits_143</t>
+        </is>
+      </c>
       <c r="C41" s="1" t="n">
         <v>45340</v>
       </c>
@@ -3039,7 +3199,11 @@
       <c r="A42" t="n">
         <v>14</v>
       </c>
-      <c r="B42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Puits_143</t>
+        </is>
+      </c>
       <c r="C42" s="1" t="n">
         <v>45341</v>
       </c>
@@ -3102,7 +3266,11 @@
       <c r="A43" t="n">
         <v>14</v>
       </c>
-      <c r="B43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Puits_143</t>
+        </is>
+      </c>
       <c r="C43" s="1" t="n">
         <v>45341</v>
       </c>
@@ -3165,7 +3333,11 @@
       <c r="A44" t="n">
         <v>15</v>
       </c>
-      <c r="B44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Puits_16</t>
+        </is>
+      </c>
       <c r="C44" s="1" t="n">
         <v>45342</v>
       </c>
@@ -3228,7 +3400,11 @@
       <c r="A45" t="n">
         <v>15</v>
       </c>
-      <c r="B45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Puits_16</t>
+        </is>
+      </c>
       <c r="C45" s="1" t="n">
         <v>45342</v>
       </c>
@@ -3291,7 +3467,11 @@
       <c r="A46" t="n">
         <v>15</v>
       </c>
-      <c r="B46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Puits_16</t>
+        </is>
+      </c>
       <c r="C46" s="1" t="n">
         <v>45343</v>
       </c>
@@ -3354,7 +3534,11 @@
       <c r="A47" t="n">
         <v>16</v>
       </c>
-      <c r="B47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Puits_213</t>
+        </is>
+      </c>
       <c r="C47" s="1" t="n">
         <v>45342</v>
       </c>
@@ -3417,7 +3601,11 @@
       <c r="A48" t="n">
         <v>16</v>
       </c>
-      <c r="B48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Puits_213</t>
+        </is>
+      </c>
       <c r="C48" s="1" t="n">
         <v>45343</v>
       </c>
@@ -3480,7 +3668,11 @@
       <c r="A49" t="n">
         <v>16</v>
       </c>
-      <c r="B49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Puits_213</t>
+        </is>
+      </c>
       <c r="C49" s="1" t="n">
         <v>45343</v>
       </c>
@@ -3543,7 +3735,11 @@
       <c r="A50" t="n">
         <v>17</v>
       </c>
-      <c r="B50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Puits_21</t>
+        </is>
+      </c>
       <c r="C50" s="1" t="n">
         <v>45344</v>
       </c>
@@ -3606,7 +3802,11 @@
       <c r="A51" t="n">
         <v>17</v>
       </c>
-      <c r="B51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Puits_21</t>
+        </is>
+      </c>
       <c r="C51" s="1" t="n">
         <v>45344</v>
       </c>
@@ -3669,7 +3869,11 @@
       <c r="A52" t="n">
         <v>17</v>
       </c>
-      <c r="B52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Puits_21</t>
+        </is>
+      </c>
       <c r="C52" s="1" t="n">
         <v>45344</v>
       </c>
@@ -3732,7 +3936,11 @@
       <c r="A53" t="n">
         <v>18</v>
       </c>
-      <c r="B53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Puits_207</t>
+        </is>
+      </c>
       <c r="C53" s="1" t="n">
         <v>45344</v>
       </c>
@@ -3795,7 +4003,11 @@
       <c r="A54" t="n">
         <v>18</v>
       </c>
-      <c r="B54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Puits_207</t>
+        </is>
+      </c>
       <c r="C54" s="1" t="n">
         <v>45345</v>
       </c>
@@ -3858,7 +4070,11 @@
       <c r="A55" t="n">
         <v>18</v>
       </c>
-      <c r="B55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Puits_207</t>
+        </is>
+      </c>
       <c r="C55" s="1" t="n">
         <v>45345</v>
       </c>
@@ -3921,7 +4137,11 @@
       <c r="A56" t="n">
         <v>19</v>
       </c>
-      <c r="B56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Puits_202</t>
+        </is>
+      </c>
       <c r="C56" s="1" t="n">
         <v>45345</v>
       </c>
@@ -3984,7 +4204,11 @@
       <c r="A57" t="n">
         <v>19</v>
       </c>
-      <c r="B57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Puits_202</t>
+        </is>
+      </c>
       <c r="C57" s="1" t="n">
         <v>45345</v>
       </c>
@@ -4047,7 +4271,11 @@
       <c r="A58" t="n">
         <v>19</v>
       </c>
-      <c r="B58" t="inlineStr"/>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Puits_202</t>
+        </is>
+      </c>
       <c r="C58" s="1" t="n">
         <v>45346</v>
       </c>
@@ -4110,7 +4338,11 @@
       <c r="A59" t="n">
         <v>20</v>
       </c>
-      <c r="B59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Puits_212</t>
+        </is>
+      </c>
       <c r="C59" s="1" t="n">
         <v>45346</v>
       </c>
@@ -4173,7 +4405,11 @@
       <c r="A60" t="n">
         <v>20</v>
       </c>
-      <c r="B60" t="inlineStr"/>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Puits_212</t>
+        </is>
+      </c>
       <c r="C60" s="1" t="n">
         <v>45347</v>
       </c>
@@ -4236,7 +4472,11 @@
       <c r="A61" t="n">
         <v>20</v>
       </c>
-      <c r="B61" t="inlineStr"/>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Puits_212</t>
+        </is>
+      </c>
       <c r="C61" s="1" t="n">
         <v>45347</v>
       </c>
@@ -4299,7 +4539,11 @@
       <c r="A62" t="n">
         <v>21</v>
       </c>
-      <c r="B62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Puits_10</t>
+        </is>
+      </c>
       <c r="C62" s="1" t="n">
         <v>45347</v>
       </c>
@@ -4362,7 +4606,11 @@
       <c r="A63" t="n">
         <v>21</v>
       </c>
-      <c r="B63" t="inlineStr"/>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Puits_10</t>
+        </is>
+      </c>
       <c r="C63" s="1" t="n">
         <v>45347</v>
       </c>
@@ -4425,7 +4673,11 @@
       <c r="A64" t="n">
         <v>21</v>
       </c>
-      <c r="B64" t="inlineStr"/>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Puits_10</t>
+        </is>
+      </c>
       <c r="C64" s="1" t="n">
         <v>45347</v>
       </c>
@@ -4488,7 +4740,11 @@
       <c r="A65" t="n">
         <v>22</v>
       </c>
-      <c r="B65" t="inlineStr"/>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Puits_217</t>
+        </is>
+      </c>
       <c r="C65" s="1" t="n">
         <v>45349</v>
       </c>
@@ -4549,7 +4805,11 @@
       <c r="A66" t="n">
         <v>22</v>
       </c>
-      <c r="B66" t="inlineStr"/>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Puits_217</t>
+        </is>
+      </c>
       <c r="C66" s="1" t="n">
         <v>45349</v>
       </c>
@@ -4610,7 +4870,11 @@
       <c r="A67" t="n">
         <v>22</v>
       </c>
-      <c r="B67" t="inlineStr"/>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Puits_217</t>
+        </is>
+      </c>
       <c r="C67" s="1" t="n">
         <v>45349</v>
       </c>
@@ -4671,7 +4935,11 @@
       <c r="A68" t="n">
         <v>23</v>
       </c>
-      <c r="B68" t="inlineStr"/>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Puits_81</t>
+        </is>
+      </c>
       <c r="C68" s="1" t="n">
         <v>45349</v>
       </c>
@@ -4734,7 +5002,11 @@
       <c r="A69" t="n">
         <v>23</v>
       </c>
-      <c r="B69" t="inlineStr"/>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Puits_81</t>
+        </is>
+      </c>
       <c r="C69" s="1" t="n">
         <v>45349</v>
       </c>
@@ -4797,7 +5069,11 @@
       <c r="A70" t="n">
         <v>23</v>
       </c>
-      <c r="B70" t="inlineStr"/>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Puits_81</t>
+        </is>
+      </c>
       <c r="C70" s="1" t="n">
         <v>44985</v>
       </c>
@@ -4860,7 +5136,11 @@
       <c r="A71" t="n">
         <v>24</v>
       </c>
-      <c r="B71" t="inlineStr"/>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Puits_170</t>
+        </is>
+      </c>
       <c r="C71" s="1" t="n">
         <v>45350</v>
       </c>
@@ -4923,7 +5203,11 @@
       <c r="A72" t="n">
         <v>24</v>
       </c>
-      <c r="B72" t="inlineStr"/>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Puits_170</t>
+        </is>
+      </c>
       <c r="C72" s="1" t="n">
         <v>45350</v>
       </c>
@@ -4986,7 +5270,11 @@
       <c r="A73" t="n">
         <v>24</v>
       </c>
-      <c r="B73" t="inlineStr"/>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Puits_170</t>
+        </is>
+      </c>
       <c r="C73" s="1" t="n">
         <v>45351</v>
       </c>
@@ -5047,7 +5335,11 @@
       <c r="A74" t="n">
         <v>25</v>
       </c>
-      <c r="B74" t="inlineStr"/>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Puits_23</t>
+        </is>
+      </c>
       <c r="C74" s="1" t="n">
         <v>45351</v>
       </c>
@@ -5110,7 +5402,11 @@
       <c r="A75" t="n">
         <v>25</v>
       </c>
-      <c r="B75" t="inlineStr"/>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Puits_23</t>
+        </is>
+      </c>
       <c r="C75" s="1" t="n">
         <v>45351</v>
       </c>
@@ -5173,7 +5469,11 @@
       <c r="A76" t="n">
         <v>25</v>
       </c>
-      <c r="B76" t="inlineStr"/>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Puits_23</t>
+        </is>
+      </c>
       <c r="C76" s="1" t="n">
         <v>45352</v>
       </c>
@@ -5236,7 +5536,11 @@
       <c r="A77" t="n">
         <v>26</v>
       </c>
-      <c r="B77" t="inlineStr"/>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Puits_24</t>
+        </is>
+      </c>
       <c r="C77" s="1" t="n">
         <v>45352</v>
       </c>
@@ -5299,7 +5603,11 @@
       <c r="A78" t="n">
         <v>26</v>
       </c>
-      <c r="B78" t="inlineStr"/>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Puits_24</t>
+        </is>
+      </c>
       <c r="C78" s="1" t="n">
         <v>45352</v>
       </c>
@@ -5362,7 +5670,11 @@
       <c r="A79" t="n">
         <v>26</v>
       </c>
-      <c r="B79" t="inlineStr"/>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Puits_24</t>
+        </is>
+      </c>
       <c r="C79" s="1" t="n">
         <v>45352</v>
       </c>
@@ -5425,7 +5737,11 @@
       <c r="A80" t="n">
         <v>27</v>
       </c>
-      <c r="B80" t="inlineStr"/>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Puits_193</t>
+        </is>
+      </c>
       <c r="C80" s="1" t="n">
         <v>45353</v>
       </c>
@@ -5488,7 +5804,11 @@
       <c r="A81" t="n">
         <v>27</v>
       </c>
-      <c r="B81" t="inlineStr"/>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Puits_193</t>
+        </is>
+      </c>
       <c r="C81" s="1" t="n">
         <v>45353</v>
       </c>
@@ -5551,7 +5871,11 @@
       <c r="A82" t="n">
         <v>27</v>
       </c>
-      <c r="B82" t="inlineStr"/>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Puits_193</t>
+        </is>
+      </c>
       <c r="C82" s="1" t="n">
         <v>45354</v>
       </c>
@@ -5614,7 +5938,11 @@
       <c r="A83" t="n">
         <v>28</v>
       </c>
-      <c r="B83" t="inlineStr"/>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Puits_29</t>
+        </is>
+      </c>
       <c r="C83" s="1" t="n">
         <v>45355</v>
       </c>
@@ -5677,7 +6005,11 @@
       <c r="A84" t="n">
         <v>28</v>
       </c>
-      <c r="B84" t="inlineStr"/>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Puits_29</t>
+        </is>
+      </c>
       <c r="C84" s="1" t="n">
         <v>45355</v>
       </c>
@@ -5740,7 +6072,11 @@
       <c r="A85" t="n">
         <v>28</v>
       </c>
-      <c r="B85" t="inlineStr"/>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Puits_29</t>
+        </is>
+      </c>
       <c r="C85" s="1" t="n">
         <v>45355</v>
       </c>
@@ -5803,7 +6139,11 @@
       <c r="A86" t="n">
         <v>29</v>
       </c>
-      <c r="B86" t="inlineStr"/>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Puits_198</t>
+        </is>
+      </c>
       <c r="C86" s="1" t="n">
         <v>45356</v>
       </c>
@@ -5866,7 +6206,11 @@
       <c r="A87" t="n">
         <v>29</v>
       </c>
-      <c r="B87" t="inlineStr"/>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Puits_198</t>
+        </is>
+      </c>
       <c r="C87" s="1" t="n">
         <v>45357</v>
       </c>
@@ -5929,7 +6273,11 @@
       <c r="A88" t="n">
         <v>29</v>
       </c>
-      <c r="B88" t="inlineStr"/>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Puits_198</t>
+        </is>
+      </c>
       <c r="C88" s="1" t="n">
         <v>45357</v>
       </c>
@@ -5992,7 +6340,11 @@
       <c r="A89" t="n">
         <v>30</v>
       </c>
-      <c r="B89" t="inlineStr"/>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Puits_182</t>
+        </is>
+      </c>
       <c r="C89" s="1" t="n">
         <v>45359</v>
       </c>
@@ -6055,7 +6407,11 @@
       <c r="A90" t="n">
         <v>30</v>
       </c>
-      <c r="B90" t="inlineStr"/>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Puits_182</t>
+        </is>
+      </c>
       <c r="C90" s="1" t="n">
         <v>45359</v>
       </c>
@@ -6118,7 +6474,11 @@
       <c r="A91" t="n">
         <v>30</v>
       </c>
-      <c r="B91" t="inlineStr"/>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Puits_182</t>
+        </is>
+      </c>
       <c r="C91" s="1" t="n">
         <v>45359</v>
       </c>
@@ -6181,7 +6541,11 @@
       <c r="A92" t="n">
         <v>31</v>
       </c>
-      <c r="B92" t="inlineStr"/>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Puits_112</t>
+        </is>
+      </c>
       <c r="C92" s="1" t="n">
         <v>45359</v>
       </c>
@@ -6244,7 +6608,11 @@
       <c r="A93" t="n">
         <v>31</v>
       </c>
-      <c r="B93" t="inlineStr"/>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Puits_112</t>
+        </is>
+      </c>
       <c r="C93" s="1" t="n">
         <v>45359</v>
       </c>
@@ -6307,7 +6675,11 @@
       <c r="A94" t="n">
         <v>31</v>
       </c>
-      <c r="B94" t="inlineStr"/>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Puits_112</t>
+        </is>
+      </c>
       <c r="C94" s="1" t="n">
         <v>45360</v>
       </c>
@@ -6370,7 +6742,11 @@
       <c r="A95" t="n">
         <v>32</v>
       </c>
-      <c r="B95" t="inlineStr"/>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Puits_168</t>
+        </is>
+      </c>
       <c r="C95" s="1" t="n">
         <v>45360</v>
       </c>
@@ -6433,7 +6809,11 @@
       <c r="A96" t="n">
         <v>32</v>
       </c>
-      <c r="B96" t="inlineStr"/>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Puits_168</t>
+        </is>
+      </c>
       <c r="C96" s="1" t="n">
         <v>45360</v>
       </c>
@@ -6496,7 +6876,11 @@
       <c r="A97" t="n">
         <v>32</v>
       </c>
-      <c r="B97" t="inlineStr"/>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Puits_168</t>
+        </is>
+      </c>
       <c r="C97" s="1" t="n">
         <v>45360</v>
       </c>
@@ -6559,7 +6943,11 @@
       <c r="A98" t="n">
         <v>33</v>
       </c>
-      <c r="B98" t="inlineStr"/>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Puits_40</t>
+        </is>
+      </c>
       <c r="C98" s="1" t="n">
         <v>45361</v>
       </c>
@@ -6622,7 +7010,11 @@
       <c r="A99" t="n">
         <v>33</v>
       </c>
-      <c r="B99" t="inlineStr"/>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Puits_40</t>
+        </is>
+      </c>
       <c r="C99" s="1" t="n">
         <v>45361</v>
       </c>
@@ -6685,7 +7077,11 @@
       <c r="A100" t="n">
         <v>33</v>
       </c>
-      <c r="B100" t="inlineStr"/>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Puits_40</t>
+        </is>
+      </c>
       <c r="C100" s="1" t="n">
         <v>45361</v>
       </c>
@@ -6748,7 +7144,11 @@
       <c r="A101" t="n">
         <v>34</v>
       </c>
-      <c r="B101" t="inlineStr"/>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Puits_192</t>
+        </is>
+      </c>
       <c r="C101" s="1" t="n">
         <v>45362</v>
       </c>
@@ -6811,7 +7211,11 @@
       <c r="A102" t="n">
         <v>34</v>
       </c>
-      <c r="B102" t="inlineStr"/>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Puits_192</t>
+        </is>
+      </c>
       <c r="C102" s="1" t="n">
         <v>45362</v>
       </c>
@@ -6874,7 +7278,11 @@
       <c r="A103" t="n">
         <v>34</v>
       </c>
-      <c r="B103" t="inlineStr"/>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Puits_192</t>
+        </is>
+      </c>
       <c r="C103" s="1" t="n">
         <v>45362</v>
       </c>
@@ -6937,7 +7345,11 @@
       <c r="A104" t="n">
         <v>35</v>
       </c>
-      <c r="B104" t="inlineStr"/>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Puits_36</t>
+        </is>
+      </c>
       <c r="C104" s="1" t="n">
         <v>45363</v>
       </c>
@@ -7000,7 +7412,11 @@
       <c r="A105" t="n">
         <v>35</v>
       </c>
-      <c r="B105" t="inlineStr"/>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Puits_36</t>
+        </is>
+      </c>
       <c r="C105" s="1" t="n">
         <v>45363</v>
       </c>
@@ -7063,7 +7479,11 @@
       <c r="A106" t="n">
         <v>35</v>
       </c>
-      <c r="B106" t="inlineStr"/>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Puits_36</t>
+        </is>
+      </c>
       <c r="C106" s="1" t="n">
         <v>45363</v>
       </c>
@@ -7126,7 +7546,11 @@
       <c r="A107" t="n">
         <v>36</v>
       </c>
-      <c r="B107" t="inlineStr"/>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Puits_113</t>
+        </is>
+      </c>
       <c r="C107" s="1" t="n">
         <v>45363</v>
       </c>
@@ -7189,7 +7613,11 @@
       <c r="A108" t="n">
         <v>36</v>
       </c>
-      <c r="B108" t="inlineStr"/>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Puits_113</t>
+        </is>
+      </c>
       <c r="C108" s="1" t="n">
         <v>45363</v>
       </c>
@@ -7252,7 +7680,11 @@
       <c r="A109" t="n">
         <v>36</v>
       </c>
-      <c r="B109" t="inlineStr"/>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Puits_113</t>
+        </is>
+      </c>
       <c r="C109" s="1" t="n">
         <v>45364</v>
       </c>
@@ -7315,7 +7747,11 @@
       <c r="A110" t="n">
         <v>37</v>
       </c>
-      <c r="B110" t="inlineStr"/>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Puits_156</t>
+        </is>
+      </c>
       <c r="C110" s="1" t="n">
         <v>45364</v>
       </c>
@@ -7378,7 +7814,11 @@
       <c r="A111" t="n">
         <v>37</v>
       </c>
-      <c r="B111" t="inlineStr"/>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Puits_156</t>
+        </is>
+      </c>
       <c r="C111" s="1" t="n">
         <v>45364</v>
       </c>
@@ -7441,7 +7881,11 @@
       <c r="A112" t="n">
         <v>37</v>
       </c>
-      <c r="B112" t="inlineStr"/>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Puits_156</t>
+        </is>
+      </c>
       <c r="C112" s="1" t="n">
         <v>45364</v>
       </c>
@@ -7504,7 +7948,11 @@
       <c r="A113" t="n">
         <v>38</v>
       </c>
-      <c r="B113" t="inlineStr"/>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Puits_50</t>
+        </is>
+      </c>
       <c r="C113" s="1" t="n">
         <v>45365</v>
       </c>
@@ -7567,7 +8015,11 @@
       <c r="A114" t="n">
         <v>38</v>
       </c>
-      <c r="B114" t="inlineStr"/>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Puits_50</t>
+        </is>
+      </c>
       <c r="C114" s="1" t="n">
         <v>45365</v>
       </c>
@@ -7630,7 +8082,11 @@
       <c r="A115" t="n">
         <v>38</v>
       </c>
-      <c r="B115" t="inlineStr"/>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Puits_50</t>
+        </is>
+      </c>
       <c r="C115" s="1" t="n">
         <v>45365</v>
       </c>
@@ -7693,7 +8149,11 @@
       <c r="A116" t="n">
         <v>39</v>
       </c>
-      <c r="B116" t="inlineStr"/>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Puits_197</t>
+        </is>
+      </c>
       <c r="C116" s="1" t="n">
         <v>45365</v>
       </c>
@@ -7756,7 +8216,11 @@
       <c r="A117" t="n">
         <v>39</v>
       </c>
-      <c r="B117" t="inlineStr"/>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Puits_197</t>
+        </is>
+      </c>
       <c r="C117" s="1" t="n">
         <v>45366</v>
       </c>
@@ -7819,7 +8283,11 @@
       <c r="A118" t="n">
         <v>39</v>
       </c>
-      <c r="B118" t="inlineStr"/>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Puits_197</t>
+        </is>
+      </c>
       <c r="C118" s="1" t="n">
         <v>45366</v>
       </c>
@@ -7882,7 +8350,11 @@
       <c r="A119" t="n">
         <v>40</v>
       </c>
-      <c r="B119" t="inlineStr"/>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Puits_15</t>
+        </is>
+      </c>
       <c r="C119" s="1" t="n">
         <v>45366</v>
       </c>
@@ -7945,7 +8417,11 @@
       <c r="A120" t="n">
         <v>40</v>
       </c>
-      <c r="B120" t="inlineStr"/>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Puits_15</t>
+        </is>
+      </c>
       <c r="C120" s="1" t="n">
         <v>45366</v>
       </c>
@@ -8008,7 +8484,11 @@
       <c r="A121" t="n">
         <v>40</v>
       </c>
-      <c r="B121" t="inlineStr"/>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Puits_15</t>
+        </is>
+      </c>
       <c r="C121" s="1" t="n">
         <v>45366</v>
       </c>
@@ -8071,7 +8551,11 @@
       <c r="A122" t="n">
         <v>41</v>
       </c>
-      <c r="B122" t="inlineStr"/>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Puits_210</t>
+        </is>
+      </c>
       <c r="C122" s="1" t="n">
         <v>45367</v>
       </c>
@@ -8134,7 +8618,11 @@
       <c r="A123" t="n">
         <v>41</v>
       </c>
-      <c r="B123" t="inlineStr"/>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Puits_210</t>
+        </is>
+      </c>
       <c r="C123" s="1" t="n">
         <v>45368</v>
       </c>
@@ -8197,7 +8685,11 @@
       <c r="A124" t="n">
         <v>41</v>
       </c>
-      <c r="B124" t="inlineStr"/>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Puits_210</t>
+        </is>
+      </c>
       <c r="C124" s="1" t="n">
         <v>45368</v>
       </c>
@@ -8260,7 +8752,11 @@
       <c r="A125" t="n">
         <v>42</v>
       </c>
-      <c r="B125" t="inlineStr"/>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Puits_9</t>
+        </is>
+      </c>
       <c r="C125" s="1" t="n">
         <v>45367</v>
       </c>
@@ -8323,7 +8819,11 @@
       <c r="A126" t="n">
         <v>42</v>
       </c>
-      <c r="B126" t="inlineStr"/>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Puits_9</t>
+        </is>
+      </c>
       <c r="C126" s="1" t="n">
         <v>45367</v>
       </c>
@@ -8386,7 +8886,11 @@
       <c r="A127" t="n">
         <v>42</v>
       </c>
-      <c r="B127" t="inlineStr"/>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Puits_9</t>
+        </is>
+      </c>
       <c r="C127" s="1" t="n">
         <v>45367</v>
       </c>
@@ -8449,7 +8953,11 @@
       <c r="A128" t="n">
         <v>43</v>
       </c>
-      <c r="B128" t="inlineStr"/>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Puits_6</t>
+        </is>
+      </c>
       <c r="C128" s="1" t="n">
         <v>45371</v>
       </c>
@@ -8512,7 +9020,11 @@
       <c r="A129" t="n">
         <v>43</v>
       </c>
-      <c r="B129" t="inlineStr"/>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Puits_6</t>
+        </is>
+      </c>
       <c r="C129" s="1" t="n">
         <v>45371</v>
       </c>
@@ -8575,7 +9087,11 @@
       <c r="A130" t="n">
         <v>43</v>
       </c>
-      <c r="B130" t="inlineStr"/>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Puits_6</t>
+        </is>
+      </c>
       <c r="C130" s="1" t="n">
         <v>45371</v>
       </c>
@@ -8638,7 +9154,11 @@
       <c r="A131" t="n">
         <v>44</v>
       </c>
-      <c r="B131" t="inlineStr"/>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Puits_17</t>
+        </is>
+      </c>
       <c r="C131" s="1" t="n">
         <v>45373</v>
       </c>
@@ -8703,7 +9223,11 @@
       <c r="A132" t="n">
         <v>44</v>
       </c>
-      <c r="B132" t="inlineStr"/>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Puits_17</t>
+        </is>
+      </c>
       <c r="C132" s="1" t="n">
         <v>45373</v>
       </c>
@@ -8766,7 +9290,11 @@
       <c r="A133" t="n">
         <v>44</v>
       </c>
-      <c r="B133" t="inlineStr"/>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Puits_17</t>
+        </is>
+      </c>
       <c r="C133" s="1" t="n">
         <v>45373</v>
       </c>
@@ -8829,7 +9357,11 @@
       <c r="A134" t="n">
         <v>45</v>
       </c>
-      <c r="B134" t="inlineStr"/>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Puits_31</t>
+        </is>
+      </c>
       <c r="C134" s="1" t="n">
         <v>45372</v>
       </c>
@@ -8892,7 +9424,11 @@
       <c r="A135" t="n">
         <v>45</v>
       </c>
-      <c r="B135" t="inlineStr"/>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Puits_31</t>
+        </is>
+      </c>
       <c r="C135" s="1" t="n">
         <v>45372</v>
       </c>
@@ -8955,7 +9491,11 @@
       <c r="A136" t="n">
         <v>45</v>
       </c>
-      <c r="B136" t="inlineStr"/>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Puits_31</t>
+        </is>
+      </c>
       <c r="C136" s="1" t="n">
         <v>45372</v>
       </c>
@@ -9018,7 +9558,11 @@
       <c r="A137" t="n">
         <v>46</v>
       </c>
-      <c r="B137" t="inlineStr"/>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Puits_43</t>
+        </is>
+      </c>
       <c r="C137" s="1" t="n">
         <v>45370</v>
       </c>
@@ -9081,7 +9625,11 @@
       <c r="A138" t="n">
         <v>46</v>
       </c>
-      <c r="B138" t="inlineStr"/>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Puits_43</t>
+        </is>
+      </c>
       <c r="C138" s="1" t="n">
         <v>45370</v>
       </c>
@@ -9144,7 +9692,11 @@
       <c r="A139" t="n">
         <v>46</v>
       </c>
-      <c r="B139" t="inlineStr"/>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Puits_43</t>
+        </is>
+      </c>
       <c r="C139" s="1" t="n">
         <v>45370</v>
       </c>
@@ -9207,7 +9759,11 @@
       <c r="A140" t="n">
         <v>47</v>
       </c>
-      <c r="B140" t="inlineStr"/>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Puits_186</t>
+        </is>
+      </c>
       <c r="C140" s="1" t="n">
         <v>45368</v>
       </c>
@@ -9270,7 +9826,11 @@
       <c r="A141" t="n">
         <v>47</v>
       </c>
-      <c r="B141" t="inlineStr"/>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Puits_186</t>
+        </is>
+      </c>
       <c r="C141" s="1" t="n">
         <v>45368</v>
       </c>
@@ -9333,7 +9893,11 @@
       <c r="A142" t="n">
         <v>47</v>
       </c>
-      <c r="B142" t="inlineStr"/>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Puits_186</t>
+        </is>
+      </c>
       <c r="C142" s="1" t="n">
         <v>45369</v>
       </c>
@@ -9396,7 +9960,11 @@
       <c r="A143" t="n">
         <v>48</v>
       </c>
-      <c r="B143" t="inlineStr"/>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Puits_160</t>
+        </is>
+      </c>
       <c r="C143" s="1" t="n">
         <v>45374</v>
       </c>
@@ -9459,7 +10027,11 @@
       <c r="A144" t="n">
         <v>48</v>
       </c>
-      <c r="B144" t="inlineStr"/>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Puits_160</t>
+        </is>
+      </c>
       <c r="C144" s="1" t="n">
         <v>45374</v>
       </c>
@@ -9522,7 +10094,11 @@
       <c r="A145" t="n">
         <v>48</v>
       </c>
-      <c r="B145" t="inlineStr"/>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Puits_160</t>
+        </is>
+      </c>
       <c r="C145" s="1" t="n">
         <v>45374</v>
       </c>
@@ -9585,7 +10161,11 @@
       <c r="A146" t="n">
         <v>49</v>
       </c>
-      <c r="B146" t="inlineStr"/>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Puits_199</t>
+        </is>
+      </c>
       <c r="C146" s="1" t="n">
         <v>45375</v>
       </c>
@@ -9648,7 +10228,11 @@
       <c r="A147" t="n">
         <v>49</v>
       </c>
-      <c r="B147" t="inlineStr"/>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Puits_199</t>
+        </is>
+      </c>
       <c r="C147" s="1" t="n">
         <v>45375</v>
       </c>
@@ -9711,7 +10295,11 @@
       <c r="A148" t="n">
         <v>49</v>
       </c>
-      <c r="B148" t="inlineStr"/>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Puits_199</t>
+        </is>
+      </c>
       <c r="C148" s="1" t="n">
         <v>45375</v>
       </c>
@@ -9774,7 +10362,11 @@
       <c r="A149" t="n">
         <v>50</v>
       </c>
-      <c r="B149" t="inlineStr"/>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Puits_205</t>
+        </is>
+      </c>
       <c r="C149" s="1" t="n">
         <v>45376</v>
       </c>
@@ -9825,7 +10417,11 @@
       <c r="A150" t="n">
         <v>50</v>
       </c>
-      <c r="B150" t="inlineStr"/>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Puits_205</t>
+        </is>
+      </c>
       <c r="C150" s="1" t="n">
         <v>45376</v>
       </c>
@@ -9876,7 +10472,11 @@
       <c r="A151" t="n">
         <v>50</v>
       </c>
-      <c r="B151" t="inlineStr"/>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Puits_205</t>
+        </is>
+      </c>
       <c r="C151" s="1" t="n">
         <v>45376</v>
       </c>
@@ -9927,7 +10527,11 @@
       <c r="A152" t="n">
         <v>51</v>
       </c>
-      <c r="B152" t="inlineStr"/>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Puits_173</t>
+        </is>
+      </c>
       <c r="C152" s="1" t="n">
         <v>45376</v>
       </c>
@@ -9990,7 +10594,11 @@
       <c r="A153" t="n">
         <v>51</v>
       </c>
-      <c r="B153" t="inlineStr"/>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Puits_173</t>
+        </is>
+      </c>
       <c r="C153" s="1" t="n">
         <v>45376</v>
       </c>
@@ -10053,7 +10661,11 @@
       <c r="A154" t="n">
         <v>51</v>
       </c>
-      <c r="B154" t="inlineStr"/>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Puits_173</t>
+        </is>
+      </c>
       <c r="C154" s="1" t="n">
         <v>45376</v>
       </c>
@@ -10116,7 +10728,11 @@
       <c r="A155" t="n">
         <v>52</v>
       </c>
-      <c r="B155" t="inlineStr"/>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Puits_53</t>
+        </is>
+      </c>
       <c r="C155" s="1" t="n">
         <v>45377</v>
       </c>
@@ -10179,7 +10795,11 @@
       <c r="A156" t="n">
         <v>52</v>
       </c>
-      <c r="B156" t="inlineStr"/>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Puits_53</t>
+        </is>
+      </c>
       <c r="C156" s="1" t="n">
         <v>45377</v>
       </c>
@@ -10242,7 +10862,11 @@
       <c r="A157" t="n">
         <v>52</v>
       </c>
-      <c r="B157" t="inlineStr"/>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Puits_53</t>
+        </is>
+      </c>
       <c r="C157" s="1" t="n">
         <v>45378</v>
       </c>
@@ -10301,7 +10925,11 @@
       <c r="A158" t="n">
         <v>53</v>
       </c>
-      <c r="B158" t="inlineStr"/>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Puits_59</t>
+        </is>
+      </c>
       <c r="C158" s="1" t="n">
         <v>45379</v>
       </c>
@@ -10364,7 +10992,11 @@
       <c r="A159" t="n">
         <v>53</v>
       </c>
-      <c r="B159" t="inlineStr"/>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Puits_59</t>
+        </is>
+      </c>
       <c r="C159" s="1" t="n">
         <v>45379</v>
       </c>
@@ -10427,7 +11059,11 @@
       <c r="A160" t="n">
         <v>53</v>
       </c>
-      <c r="B160" t="inlineStr"/>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Puits_59</t>
+        </is>
+      </c>
       <c r="C160" s="1" t="n">
         <v>45379</v>
       </c>
@@ -10490,7 +11126,11 @@
       <c r="A161" t="n">
         <v>54</v>
       </c>
-      <c r="B161" t="inlineStr"/>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Puits_46</t>
+        </is>
+      </c>
       <c r="C161" s="1" t="n">
         <v>45380</v>
       </c>
@@ -10553,7 +11193,11 @@
       <c r="A162" t="n">
         <v>54</v>
       </c>
-      <c r="B162" t="inlineStr"/>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Puits_46</t>
+        </is>
+      </c>
       <c r="C162" s="1" t="n">
         <v>45380</v>
       </c>
@@ -10616,7 +11260,11 @@
       <c r="A163" t="n">
         <v>54</v>
       </c>
-      <c r="B163" t="inlineStr"/>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Puits_46</t>
+        </is>
+      </c>
       <c r="C163" s="1" t="n">
         <v>45380</v>
       </c>
@@ -10679,7 +11327,11 @@
       <c r="A164" t="n">
         <v>55</v>
       </c>
-      <c r="B164" t="inlineStr"/>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Puits_125</t>
+        </is>
+      </c>
       <c r="C164" s="1" t="n">
         <v>45381</v>
       </c>
@@ -10742,7 +11394,11 @@
       <c r="A165" t="n">
         <v>55</v>
       </c>
-      <c r="B165" t="inlineStr"/>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Puits_125</t>
+        </is>
+      </c>
       <c r="C165" s="1" t="n">
         <v>45381</v>
       </c>
@@ -10805,7 +11461,11 @@
       <c r="A166" t="n">
         <v>55</v>
       </c>
-      <c r="B166" t="inlineStr"/>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Puits_125</t>
+        </is>
+      </c>
       <c r="C166" s="1" t="n">
         <v>45381</v>
       </c>
@@ -10868,7 +11528,11 @@
       <c r="A167" t="n">
         <v>56</v>
       </c>
-      <c r="B167" t="inlineStr"/>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Puits_169</t>
+        </is>
+      </c>
       <c r="C167" s="1" t="n">
         <v>45382</v>
       </c>
@@ -10931,7 +11595,11 @@
       <c r="A168" t="n">
         <v>56</v>
       </c>
-      <c r="B168" t="inlineStr"/>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Puits_169</t>
+        </is>
+      </c>
       <c r="C168" s="1" t="n">
         <v>45382</v>
       </c>
@@ -10994,7 +11662,11 @@
       <c r="A169" t="n">
         <v>56</v>
       </c>
-      <c r="B169" t="inlineStr"/>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Puits_169</t>
+        </is>
+      </c>
       <c r="C169" s="1" t="n">
         <v>45382</v>
       </c>
@@ -11057,7 +11729,11 @@
       <c r="A170" t="n">
         <v>57</v>
       </c>
-      <c r="B170" t="inlineStr"/>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Puits_30</t>
+        </is>
+      </c>
       <c r="C170" s="1" t="n">
         <v>45383</v>
       </c>
@@ -11120,7 +11796,11 @@
       <c r="A171" t="n">
         <v>57</v>
       </c>
-      <c r="B171" t="inlineStr"/>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Puits_30</t>
+        </is>
+      </c>
       <c r="C171" s="1" t="n">
         <v>45383</v>
       </c>
@@ -11183,7 +11863,11 @@
       <c r="A172" t="n">
         <v>57</v>
       </c>
-      <c r="B172" t="inlineStr"/>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Puits_30</t>
+        </is>
+      </c>
       <c r="C172" s="1" t="n">
         <v>45383</v>
       </c>
@@ -11246,7 +11930,11 @@
       <c r="A173" t="n">
         <v>58</v>
       </c>
-      <c r="B173" t="inlineStr"/>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Puits_25</t>
+        </is>
+      </c>
       <c r="C173" s="1" t="n">
         <v>45384</v>
       </c>
@@ -11309,7 +11997,11 @@
       <c r="A174" t="n">
         <v>58</v>
       </c>
-      <c r="B174" t="inlineStr"/>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Puits_25</t>
+        </is>
+      </c>
       <c r="C174" s="1" t="n">
         <v>45384</v>
       </c>
@@ -11372,7 +12064,11 @@
       <c r="A175" t="n">
         <v>58</v>
       </c>
-      <c r="B175" t="inlineStr"/>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Puits_25</t>
+        </is>
+      </c>
       <c r="C175" s="1" t="n">
         <v>45384</v>
       </c>
@@ -11435,7 +12131,11 @@
       <c r="A176" t="n">
         <v>59</v>
       </c>
-      <c r="B176" t="inlineStr"/>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Puits_187</t>
+        </is>
+      </c>
       <c r="C176" s="1" t="n">
         <v>45385</v>
       </c>
@@ -11498,7 +12198,11 @@
       <c r="A177" t="n">
         <v>59</v>
       </c>
-      <c r="B177" t="inlineStr"/>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Puits_187</t>
+        </is>
+      </c>
       <c r="C177" s="1" t="n">
         <v>45385</v>
       </c>
@@ -11561,7 +12265,11 @@
       <c r="A178" t="n">
         <v>59</v>
       </c>
-      <c r="B178" t="inlineStr"/>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Puits_187</t>
+        </is>
+      </c>
       <c r="C178" s="1" t="n">
         <v>45385</v>
       </c>
@@ -11624,7 +12332,11 @@
       <c r="A179" t="n">
         <v>60</v>
       </c>
-      <c r="B179" t="inlineStr"/>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Puits_38</t>
+        </is>
+      </c>
       <c r="C179" s="1" t="n">
         <v>45386</v>
       </c>
@@ -11683,7 +12395,11 @@
       <c r="A180" t="n">
         <v>60</v>
       </c>
-      <c r="B180" t="inlineStr"/>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Puits_38</t>
+        </is>
+      </c>
       <c r="C180" s="1" t="n">
         <v>45386</v>
       </c>
@@ -11742,7 +12458,11 @@
       <c r="A181" t="n">
         <v>60</v>
       </c>
-      <c r="B181" t="inlineStr"/>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Puits_38</t>
+        </is>
+      </c>
       <c r="C181" s="1" t="n">
         <v>45386</v>
       </c>
@@ -11801,7 +12521,11 @@
       <c r="A182" t="n">
         <v>61</v>
       </c>
-      <c r="B182" t="inlineStr"/>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Puits_183</t>
+        </is>
+      </c>
       <c r="C182" s="1" t="n">
         <v>45387</v>
       </c>
@@ -11864,7 +12588,11 @@
       <c r="A183" t="n">
         <v>61</v>
       </c>
-      <c r="B183" t="inlineStr"/>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Puits_183</t>
+        </is>
+      </c>
       <c r="C183" s="1" t="n">
         <v>45387</v>
       </c>
@@ -11927,7 +12655,11 @@
       <c r="A184" t="n">
         <v>61</v>
       </c>
-      <c r="B184" t="inlineStr"/>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Puits_183</t>
+        </is>
+      </c>
       <c r="C184" s="1" t="n">
         <v>45387</v>
       </c>
@@ -11990,7 +12722,11 @@
       <c r="A185" t="n">
         <v>62</v>
       </c>
-      <c r="B185" t="inlineStr"/>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Puits_196</t>
+        </is>
+      </c>
       <c r="C185" s="1" t="n">
         <v>45388</v>
       </c>
@@ -12053,7 +12789,11 @@
       <c r="A186" t="n">
         <v>62</v>
       </c>
-      <c r="B186" t="inlineStr"/>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Puits_196</t>
+        </is>
+      </c>
       <c r="C186" s="1" t="n">
         <v>45388</v>
       </c>
@@ -12116,7 +12856,11 @@
       <c r="A187" t="n">
         <v>62</v>
       </c>
-      <c r="B187" t="inlineStr"/>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Puits_196</t>
+        </is>
+      </c>
       <c r="C187" s="1" t="n">
         <v>45388</v>
       </c>
@@ -12179,7 +12923,11 @@
       <c r="A188" t="n">
         <v>63</v>
       </c>
-      <c r="B188" t="inlineStr"/>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Puits_176</t>
+        </is>
+      </c>
       <c r="C188" s="1" t="n">
         <v>45389</v>
       </c>
@@ -12242,7 +12990,11 @@
       <c r="A189" t="n">
         <v>63</v>
       </c>
-      <c r="B189" t="inlineStr"/>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Puits_176</t>
+        </is>
+      </c>
       <c r="C189" s="1" t="n">
         <v>45389</v>
       </c>
@@ -12305,7 +13057,11 @@
       <c r="A190" t="n">
         <v>63</v>
       </c>
-      <c r="B190" t="inlineStr"/>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Puits_176</t>
+        </is>
+      </c>
       <c r="C190" s="1" t="n">
         <v>45389</v>
       </c>
@@ -12368,7 +13124,11 @@
       <c r="A191" t="n">
         <v>64</v>
       </c>
-      <c r="B191" t="inlineStr"/>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Puits_85</t>
+        </is>
+      </c>
       <c r="C191" s="1" t="n">
         <v>45390</v>
       </c>
@@ -12431,7 +13191,11 @@
       <c r="A192" t="n">
         <v>64</v>
       </c>
-      <c r="B192" t="inlineStr"/>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Puits_85</t>
+        </is>
+      </c>
       <c r="C192" s="1" t="n">
         <v>45390</v>
       </c>
@@ -12494,7 +13258,11 @@
       <c r="A193" t="n">
         <v>64</v>
       </c>
-      <c r="B193" t="inlineStr"/>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Puits_85</t>
+        </is>
+      </c>
       <c r="C193" s="1" t="n">
         <v>45390</v>
       </c>
@@ -12557,7 +13325,11 @@
       <c r="A194" t="n">
         <v>65</v>
       </c>
-      <c r="B194" t="inlineStr"/>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Puits_83</t>
+        </is>
+      </c>
       <c r="C194" s="1" t="n">
         <v>45393</v>
       </c>
@@ -12620,7 +13392,11 @@
       <c r="A195" t="n">
         <v>65</v>
       </c>
-      <c r="B195" t="inlineStr"/>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Puits_83</t>
+        </is>
+      </c>
       <c r="C195" s="1" t="n">
         <v>45393</v>
       </c>
@@ -12683,7 +13459,11 @@
       <c r="A196" t="n">
         <v>65</v>
       </c>
-      <c r="B196" t="inlineStr"/>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Puits_83</t>
+        </is>
+      </c>
       <c r="C196" s="1" t="n">
         <v>45393</v>
       </c>
@@ -12746,7 +13526,11 @@
       <c r="A197" t="n">
         <v>66</v>
       </c>
-      <c r="B197" t="inlineStr"/>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Puits_231</t>
+        </is>
+      </c>
       <c r="C197" s="1" t="n">
         <v>45396</v>
       </c>
@@ -12809,7 +13593,11 @@
       <c r="A198" t="n">
         <v>66</v>
       </c>
-      <c r="B198" t="inlineStr"/>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Puits_231</t>
+        </is>
+      </c>
       <c r="C198" s="1" t="n">
         <v>45396</v>
       </c>
@@ -12872,7 +13660,11 @@
       <c r="A199" t="n">
         <v>66</v>
       </c>
-      <c r="B199" t="inlineStr"/>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Puits_231</t>
+        </is>
+      </c>
       <c r="C199" s="1" t="n">
         <v>45396</v>
       </c>
@@ -12935,7 +13727,11 @@
       <c r="A200" t="n">
         <v>67</v>
       </c>
-      <c r="B200" t="inlineStr"/>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Puits_63</t>
+        </is>
+      </c>
       <c r="C200" s="1" t="n">
         <v>45397</v>
       </c>
@@ -13000,7 +13796,11 @@
       <c r="A201" t="n">
         <v>67</v>
       </c>
-      <c r="B201" t="inlineStr"/>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Puits_63</t>
+        </is>
+      </c>
       <c r="C201" s="1" t="n">
         <v>45397</v>
       </c>
@@ -13065,7 +13865,11 @@
       <c r="A202" t="n">
         <v>67</v>
       </c>
-      <c r="B202" t="inlineStr"/>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Puits_63</t>
+        </is>
+      </c>
       <c r="C202" s="1" t="n">
         <v>45397</v>
       </c>
@@ -13130,7 +13934,11 @@
       <c r="A203" t="n">
         <v>68</v>
       </c>
-      <c r="B203" t="inlineStr"/>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Puits_123</t>
+        </is>
+      </c>
       <c r="C203" s="1" t="n">
         <v>45398</v>
       </c>
@@ -13195,7 +14003,11 @@
       <c r="A204" t="n">
         <v>68</v>
       </c>
-      <c r="B204" t="inlineStr"/>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Puits_123</t>
+        </is>
+      </c>
       <c r="C204" s="1" t="n">
         <v>45398</v>
       </c>
@@ -13260,7 +14072,11 @@
       <c r="A205" t="n">
         <v>68</v>
       </c>
-      <c r="B205" t="inlineStr"/>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Puits_123</t>
+        </is>
+      </c>
       <c r="C205" s="1" t="n">
         <v>45398</v>
       </c>
@@ -13325,7 +14141,11 @@
       <c r="A206" t="n">
         <v>69</v>
       </c>
-      <c r="B206" t="inlineStr"/>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Puits_167</t>
+        </is>
+      </c>
       <c r="C206" s="1" t="n">
         <v>45399</v>
       </c>
@@ -13388,7 +14208,11 @@
       <c r="A207" t="n">
         <v>69</v>
       </c>
-      <c r="B207" t="inlineStr"/>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Puits_167</t>
+        </is>
+      </c>
       <c r="C207" s="1" t="n">
         <v>45399</v>
       </c>
@@ -13451,7 +14275,11 @@
       <c r="A208" t="n">
         <v>69</v>
       </c>
-      <c r="B208" t="inlineStr"/>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Puits_167</t>
+        </is>
+      </c>
       <c r="C208" s="1" t="n">
         <v>45399</v>
       </c>
@@ -13514,7 +14342,11 @@
       <c r="A209" t="n">
         <v>70</v>
       </c>
-      <c r="B209" t="inlineStr"/>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Puits_27</t>
+        </is>
+      </c>
       <c r="C209" s="1" t="n">
         <v>45400</v>
       </c>
@@ -13577,7 +14409,11 @@
       <c r="A210" t="n">
         <v>70</v>
       </c>
-      <c r="B210" t="inlineStr"/>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Puits_27</t>
+        </is>
+      </c>
       <c r="C210" s="1" t="n">
         <v>45400</v>
       </c>
@@ -13640,7 +14476,11 @@
       <c r="A211" t="n">
         <v>70</v>
       </c>
-      <c r="B211" t="inlineStr"/>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Puits_27</t>
+        </is>
+      </c>
       <c r="C211" s="1" t="n">
         <v>45400</v>
       </c>
@@ -13703,7 +14543,11 @@
       <c r="A212" t="n">
         <v>71</v>
       </c>
-      <c r="B212" t="inlineStr"/>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Puits_22</t>
+        </is>
+      </c>
       <c r="C212" s="1" t="n">
         <v>45401</v>
       </c>
@@ -13768,7 +14612,11 @@
       <c r="A213" t="n">
         <v>71</v>
       </c>
-      <c r="B213" t="inlineStr"/>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Puits_22</t>
+        </is>
+      </c>
       <c r="C213" s="1" t="n">
         <v>45401</v>
       </c>
@@ -13833,7 +14681,11 @@
       <c r="A214" t="n">
         <v>71</v>
       </c>
-      <c r="B214" t="inlineStr"/>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Puits_22</t>
+        </is>
+      </c>
       <c r="C214" s="1" t="n">
         <v>45401</v>
       </c>
@@ -13898,7 +14750,11 @@
       <c r="A215" t="n">
         <v>72</v>
       </c>
-      <c r="B215" t="inlineStr"/>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Puits_13</t>
+        </is>
+      </c>
       <c r="C215" s="1" t="n">
         <v>45402</v>
       </c>
@@ -13961,7 +14817,11 @@
       <c r="A216" t="n">
         <v>72</v>
       </c>
-      <c r="B216" t="inlineStr"/>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Puits_13</t>
+        </is>
+      </c>
       <c r="C216" s="1" t="n">
         <v>45402</v>
       </c>
@@ -14024,7 +14884,11 @@
       <c r="A217" t="n">
         <v>72</v>
       </c>
-      <c r="B217" t="inlineStr"/>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Puits_13</t>
+        </is>
+      </c>
       <c r="C217" s="1" t="n">
         <v>45402</v>
       </c>
@@ -14087,7 +14951,11 @@
       <c r="A218" t="n">
         <v>73</v>
       </c>
-      <c r="B218" t="inlineStr"/>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Puits_44</t>
+        </is>
+      </c>
       <c r="C218" s="1" t="n">
         <v>45403</v>
       </c>
@@ -14152,7 +15020,11 @@
       <c r="A219" t="n">
         <v>73</v>
       </c>
-      <c r="B219" t="inlineStr"/>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Puits_44</t>
+        </is>
+      </c>
       <c r="C219" s="1" t="n">
         <v>45403</v>
       </c>
@@ -14217,7 +15089,11 @@
       <c r="A220" t="n">
         <v>73</v>
       </c>
-      <c r="B220" t="inlineStr"/>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Puits_44</t>
+        </is>
+      </c>
       <c r="C220" s="1" t="n">
         <v>45403</v>
       </c>
@@ -14282,7 +15158,11 @@
       <c r="A221" t="n">
         <v>74</v>
       </c>
-      <c r="B221" t="inlineStr"/>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Puits_189</t>
+        </is>
+      </c>
       <c r="C221" s="1" t="n">
         <v>45404</v>
       </c>
@@ -14341,7 +15221,11 @@
       <c r="A222" t="n">
         <v>74</v>
       </c>
-      <c r="B222" t="inlineStr"/>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Puits_189</t>
+        </is>
+      </c>
       <c r="C222" s="1" t="n">
         <v>45404</v>
       </c>
@@ -14400,7 +15284,11 @@
       <c r="A223" t="n">
         <v>74</v>
       </c>
-      <c r="B223" t="inlineStr"/>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Puits_189</t>
+        </is>
+      </c>
       <c r="C223" s="1" t="n">
         <v>45404</v>
       </c>
@@ -14459,7 +15347,11 @@
       <c r="A224" t="n">
         <v>75</v>
       </c>
-      <c r="B224" t="inlineStr"/>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Puits_54</t>
+        </is>
+      </c>
       <c r="C224" s="1" t="n">
         <v>45405</v>
       </c>
@@ -14522,7 +15414,11 @@
       <c r="A225" t="n">
         <v>75</v>
       </c>
-      <c r="B225" t="inlineStr"/>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Puits_54</t>
+        </is>
+      </c>
       <c r="C225" s="1" t="n">
         <v>45405</v>
       </c>
@@ -14585,7 +15481,11 @@
       <c r="A226" t="n">
         <v>75</v>
       </c>
-      <c r="B226" t="inlineStr"/>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Puits_54</t>
+        </is>
+      </c>
       <c r="C226" s="1" t="n">
         <v>45405</v>
       </c>
@@ -14648,7 +15548,11 @@
       <c r="A227" t="n">
         <v>76</v>
       </c>
-      <c r="B227" t="inlineStr"/>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Puits_48</t>
+        </is>
+      </c>
       <c r="C227" s="1" t="n">
         <v>45406</v>
       </c>
@@ -14711,7 +15615,11 @@
       <c r="A228" t="n">
         <v>76</v>
       </c>
-      <c r="B228" t="inlineStr"/>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Puits_48</t>
+        </is>
+      </c>
       <c r="C228" s="1" t="n">
         <v>45406</v>
       </c>
@@ -14774,7 +15682,11 @@
       <c r="A229" t="n">
         <v>76</v>
       </c>
-      <c r="B229" t="inlineStr"/>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Puits_48</t>
+        </is>
+      </c>
       <c r="C229" s="1" t="n">
         <v>45406</v>
       </c>
@@ -14837,7 +15749,11 @@
       <c r="A230" t="n">
         <v>77</v>
       </c>
-      <c r="B230" t="inlineStr"/>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Puits_119</t>
+        </is>
+      </c>
       <c r="C230" s="1" t="n">
         <v>45407</v>
       </c>
@@ -14900,7 +15816,11 @@
       <c r="A231" t="n">
         <v>77</v>
       </c>
-      <c r="B231" t="inlineStr"/>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Puits_119</t>
+        </is>
+      </c>
       <c r="C231" s="1" t="n">
         <v>45407</v>
       </c>
@@ -14963,7 +15883,11 @@
       <c r="A232" t="n">
         <v>77</v>
       </c>
-      <c r="B232" t="inlineStr"/>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Puits_119</t>
+        </is>
+      </c>
       <c r="C232" s="1" t="n">
         <v>45407</v>
       </c>
@@ -15026,7 +15950,11 @@
       <c r="A233" t="n">
         <v>78</v>
       </c>
-      <c r="B233" t="inlineStr"/>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Puits_39</t>
+        </is>
+      </c>
       <c r="C233" s="1" t="n">
         <v>45408</v>
       </c>
@@ -15089,7 +16017,11 @@
       <c r="A234" t="n">
         <v>78</v>
       </c>
-      <c r="B234" t="inlineStr"/>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Puits_39</t>
+        </is>
+      </c>
       <c r="C234" s="1" t="n">
         <v>45408</v>
       </c>
@@ -15152,7 +16084,11 @@
       <c r="A235" t="n">
         <v>78</v>
       </c>
-      <c r="B235" t="inlineStr"/>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Puits_39</t>
+        </is>
+      </c>
       <c r="C235" s="1" t="n">
         <v>45408</v>
       </c>
@@ -15215,7 +16151,11 @@
       <c r="A236" t="n">
         <v>79</v>
       </c>
-      <c r="B236" t="inlineStr"/>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Puits_184</t>
+        </is>
+      </c>
       <c r="C236" s="1" t="n">
         <v>45409</v>
       </c>
@@ -15278,7 +16218,11 @@
       <c r="A237" t="n">
         <v>79</v>
       </c>
-      <c r="B237" t="inlineStr"/>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Puits_184</t>
+        </is>
+      </c>
       <c r="C237" s="1" t="n">
         <v>45409</v>
       </c>
@@ -15341,7 +16285,11 @@
       <c r="A238" t="n">
         <v>79</v>
       </c>
-      <c r="B238" t="inlineStr"/>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Puits_184</t>
+        </is>
+      </c>
       <c r="C238" s="1" t="n">
         <v>45409</v>
       </c>
@@ -15404,7 +16352,11 @@
       <c r="A239" t="n">
         <v>80</v>
       </c>
-      <c r="B239" t="inlineStr"/>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Puits_145</t>
+        </is>
+      </c>
       <c r="C239" s="1" t="n">
         <v>45410</v>
       </c>
@@ -15467,7 +16419,11 @@
       <c r="A240" t="n">
         <v>80</v>
       </c>
-      <c r="B240" t="inlineStr"/>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Puits_145</t>
+        </is>
+      </c>
       <c r="C240" s="1" t="n">
         <v>45410</v>
       </c>
@@ -15530,7 +16486,11 @@
       <c r="A241" t="n">
         <v>80</v>
       </c>
-      <c r="B241" t="inlineStr"/>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Puits_145</t>
+        </is>
+      </c>
       <c r="C241" s="1" t="n">
         <v>45410</v>
       </c>
@@ -15593,7 +16553,11 @@
       <c r="A242" t="n">
         <v>81</v>
       </c>
-      <c r="B242" t="inlineStr"/>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Puits_165</t>
+        </is>
+      </c>
       <c r="C242" s="1" t="n">
         <v>45411</v>
       </c>
@@ -15656,7 +16620,11 @@
       <c r="A243" t="n">
         <v>81</v>
       </c>
-      <c r="B243" t="inlineStr"/>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Puits_165</t>
+        </is>
+      </c>
       <c r="C243" s="1" t="n">
         <v>45411</v>
       </c>
@@ -15719,7 +16687,11 @@
       <c r="A244" t="n">
         <v>81</v>
       </c>
-      <c r="B244" t="inlineStr"/>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Puits_165</t>
+        </is>
+      </c>
       <c r="C244" s="1" t="n">
         <v>45411</v>
       </c>
@@ -15782,7 +16754,11 @@
       <c r="A245" t="n">
         <v>82</v>
       </c>
-      <c r="B245" t="inlineStr"/>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Puits_179</t>
+        </is>
+      </c>
       <c r="C245" s="1" t="n">
         <v>45413</v>
       </c>
@@ -15845,7 +16821,11 @@
       <c r="A246" t="n">
         <v>82</v>
       </c>
-      <c r="B246" t="inlineStr"/>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Puits_179</t>
+        </is>
+      </c>
       <c r="C246" s="1" t="n">
         <v>45413</v>
       </c>
@@ -15908,7 +16888,11 @@
       <c r="A247" t="n">
         <v>82</v>
       </c>
-      <c r="B247" t="inlineStr"/>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Puits_179</t>
+        </is>
+      </c>
       <c r="C247" s="1" t="n">
         <v>45413</v>
       </c>
@@ -15971,7 +16955,11 @@
       <c r="A248" t="n">
         <v>83</v>
       </c>
-      <c r="B248" t="inlineStr"/>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Puits_190</t>
+        </is>
+      </c>
       <c r="C248" s="1" t="n">
         <v>45414</v>
       </c>
@@ -16034,7 +17022,11 @@
       <c r="A249" t="n">
         <v>83</v>
       </c>
-      <c r="B249" t="inlineStr"/>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Puits_190</t>
+        </is>
+      </c>
       <c r="C249" s="1" t="n">
         <v>45414</v>
       </c>
@@ -16097,7 +17089,11 @@
       <c r="A250" t="n">
         <v>83</v>
       </c>
-      <c r="B250" t="inlineStr"/>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Puits_190</t>
+        </is>
+      </c>
       <c r="C250" s="1" t="n">
         <v>45414</v>
       </c>
@@ -16160,7 +17156,11 @@
       <c r="A251" t="n">
         <v>84</v>
       </c>
-      <c r="B251" t="inlineStr"/>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Puits_161</t>
+        </is>
+      </c>
       <c r="C251" s="1" t="n">
         <v>45415</v>
       </c>
@@ -16223,7 +17223,11 @@
       <c r="A252" t="n">
         <v>84</v>
       </c>
-      <c r="B252" t="inlineStr"/>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Puits_161</t>
+        </is>
+      </c>
       <c r="C252" s="1" t="n">
         <v>45415</v>
       </c>
@@ -16286,7 +17290,11 @@
       <c r="A253" t="n">
         <v>84</v>
       </c>
-      <c r="B253" t="inlineStr"/>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Puits_161</t>
+        </is>
+      </c>
       <c r="C253" s="1" t="n">
         <v>45415</v>
       </c>
@@ -16349,7 +17357,11 @@
       <c r="A254" t="n">
         <v>85</v>
       </c>
-      <c r="B254" t="inlineStr"/>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Puits_55</t>
+        </is>
+      </c>
       <c r="C254" s="1" t="n">
         <v>45416</v>
       </c>
@@ -16412,7 +17424,11 @@
       <c r="A255" t="n">
         <v>85</v>
       </c>
-      <c r="B255" t="inlineStr"/>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Puits_55</t>
+        </is>
+      </c>
       <c r="C255" s="1" t="n">
         <v>45416</v>
       </c>
@@ -16475,7 +17491,11 @@
       <c r="A256" t="n">
         <v>85</v>
       </c>
-      <c r="B256" t="inlineStr"/>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Puits_55</t>
+        </is>
+      </c>
       <c r="C256" s="1" t="n">
         <v>45416</v>
       </c>
@@ -16538,7 +17558,11 @@
       <c r="A257" t="n">
         <v>86</v>
       </c>
-      <c r="B257" t="inlineStr"/>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Puits_28</t>
+        </is>
+      </c>
       <c r="C257" s="1" t="n">
         <v>45417</v>
       </c>
@@ -16601,7 +17625,11 @@
       <c r="A258" t="n">
         <v>86</v>
       </c>
-      <c r="B258" t="inlineStr"/>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Puits_28</t>
+        </is>
+      </c>
       <c r="C258" s="1" t="n">
         <v>45417</v>
       </c>
@@ -16664,7 +17692,11 @@
       <c r="A259" t="n">
         <v>86</v>
       </c>
-      <c r="B259" t="inlineStr"/>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Puits_28</t>
+        </is>
+      </c>
       <c r="C259" s="1" t="n">
         <v>45417</v>
       </c>
@@ -16727,7 +17759,11 @@
       <c r="A260" t="n">
         <v>87</v>
       </c>
-      <c r="B260" t="inlineStr"/>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Puits_188</t>
+        </is>
+      </c>
       <c r="C260" s="1" t="n">
         <v>45418</v>
       </c>
@@ -16790,7 +17826,11 @@
       <c r="A261" t="n">
         <v>87</v>
       </c>
-      <c r="B261" t="inlineStr"/>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Puits_188</t>
+        </is>
+      </c>
       <c r="C261" s="1" t="n">
         <v>45418</v>
       </c>
@@ -16853,7 +17893,11 @@
       <c r="A262" t="n">
         <v>87</v>
       </c>
-      <c r="B262" t="inlineStr"/>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Puits_188</t>
+        </is>
+      </c>
       <c r="C262" s="1" t="n">
         <v>45418</v>
       </c>
@@ -16916,7 +17960,11 @@
       <c r="A263" t="n">
         <v>88</v>
       </c>
-      <c r="B263" t="inlineStr"/>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Puits_180</t>
+        </is>
+      </c>
       <c r="C263" s="1" t="n">
         <v>45419</v>
       </c>
@@ -16979,7 +18027,11 @@
       <c r="A264" t="n">
         <v>88</v>
       </c>
-      <c r="B264" t="inlineStr"/>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Puits_180</t>
+        </is>
+      </c>
       <c r="C264" s="1" t="n">
         <v>45419</v>
       </c>
@@ -17042,7 +18094,11 @@
       <c r="A265" t="n">
         <v>88</v>
       </c>
-      <c r="B265" t="inlineStr"/>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Puits_180</t>
+        </is>
+      </c>
       <c r="C265" s="1" t="n">
         <v>45419</v>
       </c>
@@ -17105,7 +18161,11 @@
       <c r="A266" t="n">
         <v>89</v>
       </c>
-      <c r="B266" t="inlineStr"/>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Puits_163</t>
+        </is>
+      </c>
       <c r="C266" s="1" t="n">
         <v>45420</v>
       </c>
@@ -17168,7 +18228,11 @@
       <c r="A267" t="n">
         <v>89</v>
       </c>
-      <c r="B267" t="inlineStr"/>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Puits_163</t>
+        </is>
+      </c>
       <c r="C267" s="1" t="n">
         <v>45420</v>
       </c>
@@ -17231,7 +18295,11 @@
       <c r="A268" t="n">
         <v>89</v>
       </c>
-      <c r="B268" t="inlineStr"/>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Puits_163</t>
+        </is>
+      </c>
       <c r="C268" s="1" t="n">
         <v>45420</v>
       </c>
@@ -17294,7 +18362,11 @@
       <c r="A269" t="n">
         <v>90</v>
       </c>
-      <c r="B269" t="inlineStr"/>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Puits_34</t>
+        </is>
+      </c>
       <c r="C269" s="1" t="n">
         <v>45421</v>
       </c>
@@ -17357,7 +18429,11 @@
       <c r="A270" t="n">
         <v>90</v>
       </c>
-      <c r="B270" t="inlineStr"/>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Puits_34</t>
+        </is>
+      </c>
       <c r="C270" s="1" t="n">
         <v>45421</v>
       </c>
@@ -17420,7 +18496,11 @@
       <c r="A271" t="n">
         <v>90</v>
       </c>
-      <c r="B271" t="inlineStr"/>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Puits_34</t>
+        </is>
+      </c>
       <c r="C271" s="1" t="n">
         <v>45421</v>
       </c>
@@ -17483,7 +18563,11 @@
       <c r="A272" t="n">
         <v>91</v>
       </c>
-      <c r="B272" t="inlineStr"/>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Puits_155</t>
+        </is>
+      </c>
       <c r="C272" s="1" t="n">
         <v>45422</v>
       </c>
@@ -17546,7 +18630,11 @@
       <c r="A273" t="n">
         <v>91</v>
       </c>
-      <c r="B273" t="inlineStr"/>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Puits_155</t>
+        </is>
+      </c>
       <c r="C273" s="1" t="n">
         <v>45422</v>
       </c>
@@ -17609,7 +18697,11 @@
       <c r="A274" t="n">
         <v>91</v>
       </c>
-      <c r="B274" t="inlineStr"/>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Puits_155</t>
+        </is>
+      </c>
       <c r="C274" s="1" t="n">
         <v>45422</v>
       </c>
@@ -17672,7 +18764,11 @@
       <c r="A275" t="n">
         <v>92</v>
       </c>
-      <c r="B275" t="inlineStr"/>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Puits_82</t>
+        </is>
+      </c>
       <c r="C275" s="1" t="n">
         <v>45424</v>
       </c>
@@ -17735,7 +18831,11 @@
       <c r="A276" t="n">
         <v>92</v>
       </c>
-      <c r="B276" t="inlineStr"/>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Puits_82</t>
+        </is>
+      </c>
       <c r="C276" s="1" t="n">
         <v>45424</v>
       </c>
@@ -17798,7 +18898,11 @@
       <c r="A277" t="n">
         <v>92</v>
       </c>
-      <c r="B277" t="inlineStr"/>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Puits_82</t>
+        </is>
+      </c>
       <c r="C277" s="1" t="n">
         <v>45424</v>
       </c>
@@ -17861,7 +18965,11 @@
       <c r="A278" t="n">
         <v>93</v>
       </c>
-      <c r="B278" t="inlineStr"/>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Puits_201</t>
+        </is>
+      </c>
       <c r="C278" s="1" t="n">
         <v>45425</v>
       </c>
@@ -17924,7 +19032,11 @@
       <c r="A279" t="n">
         <v>93</v>
       </c>
-      <c r="B279" t="inlineStr"/>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Puits_201</t>
+        </is>
+      </c>
       <c r="C279" s="1" t="n">
         <v>45425</v>
       </c>
@@ -17987,7 +19099,11 @@
       <c r="A280" t="n">
         <v>93</v>
       </c>
-      <c r="B280" t="inlineStr"/>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Puits_201</t>
+        </is>
+      </c>
       <c r="C280" s="1" t="n">
         <v>45425</v>
       </c>
@@ -18050,7 +19166,11 @@
       <c r="A281" t="n">
         <v>94</v>
       </c>
-      <c r="B281" t="inlineStr"/>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Puits_203</t>
+        </is>
+      </c>
       <c r="C281" s="1" t="n">
         <v>45427</v>
       </c>
@@ -18113,7 +19233,11 @@
       <c r="A282" t="n">
         <v>94</v>
       </c>
-      <c r="B282" t="inlineStr"/>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Puits_203</t>
+        </is>
+      </c>
       <c r="C282" s="1" t="n">
         <v>45427</v>
       </c>
@@ -18176,7 +19300,11 @@
       <c r="A283" t="n">
         <v>94</v>
       </c>
-      <c r="B283" t="inlineStr"/>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Puits_203</t>
+        </is>
+      </c>
       <c r="C283" s="1" t="n">
         <v>45427</v>
       </c>
@@ -18239,7 +19367,11 @@
       <c r="A284" t="n">
         <v>95</v>
       </c>
-      <c r="B284" t="inlineStr"/>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Puits_174</t>
+        </is>
+      </c>
       <c r="C284" s="1" t="n">
         <v>45428</v>
       </c>
@@ -18302,7 +19434,11 @@
       <c r="A285" t="n">
         <v>95</v>
       </c>
-      <c r="B285" t="inlineStr"/>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Puits_174</t>
+        </is>
+      </c>
       <c r="C285" s="1" t="n">
         <v>45428</v>
       </c>
@@ -18365,7 +19501,11 @@
       <c r="A286" t="n">
         <v>95</v>
       </c>
-      <c r="B286" t="inlineStr"/>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Puits_174</t>
+        </is>
+      </c>
       <c r="C286" s="1" t="n">
         <v>45428</v>
       </c>
@@ -18428,7 +19568,11 @@
       <c r="A287" t="n">
         <v>96</v>
       </c>
-      <c r="B287" t="inlineStr"/>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Puits_171</t>
+        </is>
+      </c>
       <c r="C287" s="1" t="n">
         <v>45429</v>
       </c>
@@ -18491,7 +19635,11 @@
       <c r="A288" t="n">
         <v>96</v>
       </c>
-      <c r="B288" t="inlineStr"/>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Puits_171</t>
+        </is>
+      </c>
       <c r="C288" s="1" t="n">
         <v>45429</v>
       </c>
@@ -18554,7 +19702,11 @@
       <c r="A289" t="n">
         <v>96</v>
       </c>
-      <c r="B289" t="inlineStr"/>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Puits_171</t>
+        </is>
+      </c>
       <c r="C289" s="1" t="n">
         <v>45429</v>
       </c>
@@ -18617,7 +19769,11 @@
       <c r="A290" t="n">
         <v>97</v>
       </c>
-      <c r="B290" t="inlineStr"/>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Puits_47</t>
+        </is>
+      </c>
       <c r="C290" s="1" t="n">
         <v>45430</v>
       </c>
@@ -18680,7 +19836,11 @@
       <c r="A291" t="n">
         <v>97</v>
       </c>
-      <c r="B291" t="inlineStr"/>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Puits_47</t>
+        </is>
+      </c>
       <c r="C291" s="1" t="n">
         <v>45430</v>
       </c>
@@ -18743,7 +19903,11 @@
       <c r="A292" t="n">
         <v>97</v>
       </c>
-      <c r="B292" t="inlineStr"/>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Puits_47</t>
+        </is>
+      </c>
       <c r="C292" s="1" t="n">
         <v>45430</v>
       </c>
@@ -18806,7 +19970,11 @@
       <c r="A293" t="n">
         <v>98</v>
       </c>
-      <c r="B293" t="inlineStr"/>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Puits_166</t>
+        </is>
+      </c>
       <c r="C293" s="1" t="n">
         <v>45431</v>
       </c>
@@ -18869,7 +20037,11 @@
       <c r="A294" t="n">
         <v>98</v>
       </c>
-      <c r="B294" t="inlineStr"/>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Puits_166</t>
+        </is>
+      </c>
       <c r="C294" s="1" t="n">
         <v>45431</v>
       </c>
@@ -18932,7 +20104,11 @@
       <c r="A295" t="n">
         <v>98</v>
       </c>
-      <c r="B295" t="inlineStr"/>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Puits_166</t>
+        </is>
+      </c>
       <c r="C295" s="1" t="n">
         <v>45431</v>
       </c>
@@ -18995,7 +20171,11 @@
       <c r="A296" t="n">
         <v>99</v>
       </c>
-      <c r="B296" t="inlineStr"/>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Puits_26</t>
+        </is>
+      </c>
       <c r="C296" s="1" t="n">
         <v>45432</v>
       </c>
@@ -19058,7 +20238,11 @@
       <c r="A297" t="n">
         <v>99</v>
       </c>
-      <c r="B297" t="inlineStr"/>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Puits_26</t>
+        </is>
+      </c>
       <c r="C297" s="1" t="n">
         <v>45432</v>
       </c>
@@ -19121,7 +20305,11 @@
       <c r="A298" t="n">
         <v>99</v>
       </c>
-      <c r="B298" t="inlineStr"/>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Puits_26</t>
+        </is>
+      </c>
       <c r="C298" s="1" t="n">
         <v>45432</v>
       </c>
@@ -19184,7 +20372,11 @@
       <c r="A299" t="n">
         <v>100</v>
       </c>
-      <c r="B299" t="inlineStr"/>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Puits_5</t>
+        </is>
+      </c>
       <c r="C299" s="1" t="n">
         <v>45433</v>
       </c>
@@ -19247,7 +20439,11 @@
       <c r="A300" t="n">
         <v>100</v>
       </c>
-      <c r="B300" t="inlineStr"/>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Puits_5</t>
+        </is>
+      </c>
       <c r="C300" s="1" t="n">
         <v>45433</v>
       </c>
@@ -19310,7 +20506,11 @@
       <c r="A301" t="n">
         <v>100</v>
       </c>
-      <c r="B301" t="inlineStr"/>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Puits_5</t>
+        </is>
+      </c>
       <c r="C301" s="1" t="n">
         <v>45433</v>
       </c>
@@ -19373,7 +20573,11 @@
       <c r="A302" t="n">
         <v>101</v>
       </c>
-      <c r="B302" t="inlineStr"/>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Puits_120</t>
+        </is>
+      </c>
       <c r="C302" s="1" t="n">
         <v>45434</v>
       </c>
@@ -19436,7 +20640,11 @@
       <c r="A303" t="n">
         <v>101</v>
       </c>
-      <c r="B303" t="inlineStr"/>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Puits_120</t>
+        </is>
+      </c>
       <c r="C303" s="1" t="n">
         <v>45434</v>
       </c>
@@ -19499,7 +20707,11 @@
       <c r="A304" t="n">
         <v>101</v>
       </c>
-      <c r="B304" t="inlineStr"/>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Puits_120</t>
+        </is>
+      </c>
       <c r="C304" s="1" t="n">
         <v>45434</v>
       </c>
@@ -19562,7 +20774,11 @@
       <c r="A305" t="n">
         <v>102</v>
       </c>
-      <c r="B305" t="inlineStr"/>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Puits_181</t>
+        </is>
+      </c>
       <c r="C305" s="1" t="n">
         <v>45435</v>
       </c>
@@ -19625,7 +20841,11 @@
       <c r="A306" t="n">
         <v>102</v>
       </c>
-      <c r="B306" t="inlineStr"/>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Puits_181</t>
+        </is>
+      </c>
       <c r="C306" s="1" t="n">
         <v>45436</v>
       </c>
@@ -19688,7 +20908,11 @@
       <c r="A307" t="n">
         <v>102</v>
       </c>
-      <c r="B307" t="inlineStr"/>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Puits_181</t>
+        </is>
+      </c>
       <c r="C307" s="1" t="n">
         <v>45436</v>
       </c>
@@ -19751,7 +20975,11 @@
       <c r="A308" t="n">
         <v>103</v>
       </c>
-      <c r="B308" t="inlineStr"/>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Puits_211</t>
+        </is>
+      </c>
       <c r="C308" s="1" t="n">
         <v>45438</v>
       </c>
@@ -19814,7 +21042,11 @@
       <c r="A309" t="n">
         <v>103</v>
       </c>
-      <c r="B309" t="inlineStr"/>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Puits_211</t>
+        </is>
+      </c>
       <c r="C309" s="1" t="n">
         <v>45438</v>
       </c>
@@ -19877,7 +21109,11 @@
       <c r="A310" t="n">
         <v>103</v>
       </c>
-      <c r="B310" t="inlineStr"/>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Puits_211</t>
+        </is>
+      </c>
       <c r="C310" s="1" t="n">
         <v>45438</v>
       </c>
@@ -19940,7 +21176,11 @@
       <c r="A311" t="n">
         <v>104</v>
       </c>
-      <c r="B311" t="inlineStr"/>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Puits_18</t>
+        </is>
+      </c>
       <c r="C311" s="1" t="n">
         <v>45439</v>
       </c>
@@ -20003,7 +21243,11 @@
       <c r="A312" t="n">
         <v>104</v>
       </c>
-      <c r="B312" t="inlineStr"/>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Puits_18</t>
+        </is>
+      </c>
       <c r="C312" s="1" t="n">
         <v>45439</v>
       </c>
@@ -20066,7 +21310,11 @@
       <c r="A313" t="n">
         <v>104</v>
       </c>
-      <c r="B313" t="inlineStr"/>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Puits_18</t>
+        </is>
+      </c>
       <c r="C313" s="1" t="n">
         <v>45439</v>
       </c>
@@ -20129,7 +21377,11 @@
       <c r="A314" t="n">
         <v>105</v>
       </c>
-      <c r="B314" t="inlineStr"/>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Puits_60</t>
+        </is>
+      </c>
       <c r="C314" s="1" t="n">
         <v>45440</v>
       </c>
@@ -20192,7 +21444,11 @@
       <c r="A315" t="n">
         <v>105</v>
       </c>
-      <c r="B315" t="inlineStr"/>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Puits_60</t>
+        </is>
+      </c>
       <c r="C315" s="1" t="n">
         <v>45441</v>
       </c>
@@ -20255,7 +21511,11 @@
       <c r="A316" t="n">
         <v>105</v>
       </c>
-      <c r="B316" t="inlineStr"/>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Puits_60</t>
+        </is>
+      </c>
       <c r="C316" s="1" t="n">
         <v>45441</v>
       </c>
@@ -20318,7 +21578,11 @@
       <c r="A317" t="n">
         <v>106</v>
       </c>
-      <c r="B317" t="inlineStr"/>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Puits_164</t>
+        </is>
+      </c>
       <c r="C317" s="1" t="n">
         <v>45442</v>
       </c>
@@ -20381,7 +21645,11 @@
       <c r="A318" t="n">
         <v>106</v>
       </c>
-      <c r="B318" t="inlineStr"/>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Puits_164</t>
+        </is>
+      </c>
       <c r="C318" s="1" t="n">
         <v>45442</v>
       </c>
@@ -20444,7 +21712,11 @@
       <c r="A319" t="n">
         <v>106</v>
       </c>
-      <c r="B319" t="inlineStr"/>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Puits_164</t>
+        </is>
+      </c>
       <c r="C319" s="1" t="n">
         <v>45442</v>
       </c>
@@ -20507,7 +21779,11 @@
       <c r="A320" t="n">
         <v>107</v>
       </c>
-      <c r="B320" t="inlineStr"/>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Puits_206</t>
+        </is>
+      </c>
       <c r="C320" s="1" t="n">
         <v>45443</v>
       </c>
@@ -20570,7 +21846,11 @@
       <c r="A321" t="n">
         <v>107</v>
       </c>
-      <c r="B321" t="inlineStr"/>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Puits_206</t>
+        </is>
+      </c>
       <c r="C321" s="1" t="n">
         <v>45443</v>
       </c>
@@ -20633,7 +21913,11 @@
       <c r="A322" t="n">
         <v>107</v>
       </c>
-      <c r="B322" t="inlineStr"/>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Puits_206</t>
+        </is>
+      </c>
       <c r="C322" s="1" t="n">
         <v>45443</v>
       </c>
@@ -20696,7 +21980,11 @@
       <c r="A323" t="n">
         <v>108</v>
       </c>
-      <c r="B323" t="inlineStr"/>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Puits_172</t>
+        </is>
+      </c>
       <c r="C323" s="1" t="n">
         <v>45444</v>
       </c>
@@ -20759,7 +22047,11 @@
       <c r="A324" t="n">
         <v>108</v>
       </c>
-      <c r="B324" t="inlineStr"/>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Puits_172</t>
+        </is>
+      </c>
       <c r="C324" s="1" t="n">
         <v>45444</v>
       </c>
@@ -20822,7 +22114,11 @@
       <c r="A325" t="n">
         <v>108</v>
       </c>
-      <c r="B325" t="inlineStr"/>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Puits_172</t>
+        </is>
+      </c>
       <c r="C325" s="1" t="n">
         <v>45444</v>
       </c>
@@ -20885,7 +22181,11 @@
       <c r="A326" t="n">
         <v>109</v>
       </c>
-      <c r="B326" t="inlineStr"/>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Puits_86</t>
+        </is>
+      </c>
       <c r="C326" s="1" t="n">
         <v>45446</v>
       </c>
@@ -20942,7 +22242,11 @@
       <c r="A327" t="n">
         <v>109</v>
       </c>
-      <c r="B327" t="inlineStr"/>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Puits_86</t>
+        </is>
+      </c>
       <c r="C327" s="1" t="n">
         <v>45446</v>
       </c>
@@ -20999,7 +22303,11 @@
       <c r="A328" t="n">
         <v>109</v>
       </c>
-      <c r="B328" t="inlineStr"/>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Puits_86</t>
+        </is>
+      </c>
       <c r="C328" s="1" t="n">
         <v>45446</v>
       </c>
@@ -21056,7 +22364,11 @@
       <c r="A329" t="n">
         <v>110</v>
       </c>
-      <c r="B329" t="inlineStr"/>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Puits_178</t>
+        </is>
+      </c>
       <c r="C329" s="1" t="n">
         <v>45447</v>
       </c>
@@ -21119,7 +22431,11 @@
       <c r="A330" t="n">
         <v>110</v>
       </c>
-      <c r="B330" t="inlineStr"/>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Puits_178</t>
+        </is>
+      </c>
       <c r="C330" s="1" t="n">
         <v>45447</v>
       </c>
@@ -21182,7 +22498,11 @@
       <c r="A331" t="n">
         <v>110</v>
       </c>
-      <c r="B331" t="inlineStr"/>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Puits_178</t>
+        </is>
+      </c>
       <c r="C331" s="1" t="n">
         <v>45447</v>
       </c>
@@ -21245,7 +22565,11 @@
       <c r="A332" t="n">
         <v>111</v>
       </c>
-      <c r="B332" t="inlineStr"/>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Puits_185</t>
+        </is>
+      </c>
       <c r="C332" s="1" t="n">
         <v>45448</v>
       </c>
@@ -21310,7 +22634,11 @@
       <c r="A333" t="n">
         <v>111</v>
       </c>
-      <c r="B333" t="inlineStr"/>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Puits_185</t>
+        </is>
+      </c>
       <c r="C333" s="1" t="n">
         <v>45448</v>
       </c>
@@ -21375,7 +22703,11 @@
       <c r="A334" t="n">
         <v>111</v>
       </c>
-      <c r="B334" t="inlineStr"/>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Puits_185</t>
+        </is>
+      </c>
       <c r="C334" s="1" t="n">
         <v>45448</v>
       </c>
@@ -21440,7 +22772,11 @@
       <c r="A335" t="n">
         <v>112</v>
       </c>
-      <c r="B335" t="inlineStr"/>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Puits_194</t>
+        </is>
+      </c>
       <c r="C335" s="1" t="n">
         <v>45449</v>
       </c>
@@ -21503,7 +22839,11 @@
       <c r="A336" t="n">
         <v>112</v>
       </c>
-      <c r="B336" t="inlineStr"/>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Puits_194</t>
+        </is>
+      </c>
       <c r="C336" s="1" t="n">
         <v>45449</v>
       </c>
@@ -21566,7 +22906,11 @@
       <c r="A337" t="n">
         <v>112</v>
       </c>
-      <c r="B337" t="inlineStr"/>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Puits_194</t>
+        </is>
+      </c>
       <c r="C337" s="1" t="n">
         <v>45449</v>
       </c>
@@ -21629,7 +22973,11 @@
       <c r="A338" t="n">
         <v>113</v>
       </c>
-      <c r="B338" t="inlineStr"/>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Puits_191</t>
+        </is>
+      </c>
       <c r="C338" s="1" t="n">
         <v>45450</v>
       </c>
@@ -21692,7 +23040,11 @@
       <c r="A339" t="n">
         <v>113</v>
       </c>
-      <c r="B339" t="inlineStr"/>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Puits_191</t>
+        </is>
+      </c>
       <c r="C339" s="1" t="n">
         <v>45450</v>
       </c>
@@ -21755,7 +23107,11 @@
       <c r="A340" t="n">
         <v>113</v>
       </c>
-      <c r="B340" t="inlineStr"/>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Puits_191</t>
+        </is>
+      </c>
       <c r="C340" s="1" t="n">
         <v>45450</v>
       </c>
@@ -21818,7 +23174,11 @@
       <c r="A341" t="n">
         <v>114</v>
       </c>
-      <c r="B341" t="inlineStr"/>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Puits_144</t>
+        </is>
+      </c>
       <c r="C341" s="1" t="n">
         <v>45451</v>
       </c>
@@ -21881,7 +23241,11 @@
       <c r="A342" t="n">
         <v>114</v>
       </c>
-      <c r="B342" t="inlineStr"/>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Puits_144</t>
+        </is>
+      </c>
       <c r="C342" s="1" t="n">
         <v>45451</v>
       </c>
@@ -21944,7 +23308,11 @@
       <c r="A343" t="n">
         <v>114</v>
       </c>
-      <c r="B343" t="inlineStr"/>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Puits_144</t>
+        </is>
+      </c>
       <c r="C343" s="1" t="n">
         <v>45451</v>
       </c>
@@ -22007,7 +23375,11 @@
       <c r="A344" t="n">
         <v>115</v>
       </c>
-      <c r="B344" t="inlineStr"/>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Puits_177</t>
+        </is>
+      </c>
       <c r="C344" s="1" t="n">
         <v>45453</v>
       </c>
@@ -22072,7 +23444,11 @@
       <c r="A345" t="n">
         <v>115</v>
       </c>
-      <c r="B345" t="inlineStr"/>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Puits_177</t>
+        </is>
+      </c>
       <c r="C345" s="1" t="n">
         <v>45453</v>
       </c>
@@ -22137,7 +23513,11 @@
       <c r="A346" t="n">
         <v>115</v>
       </c>
-      <c r="B346" t="inlineStr"/>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Puits_177</t>
+        </is>
+      </c>
       <c r="C346" s="1" t="n">
         <v>45453</v>
       </c>
@@ -22202,7 +23582,11 @@
       <c r="A347" t="n">
         <v>116</v>
       </c>
-      <c r="B347" t="inlineStr"/>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Puits_45</t>
+        </is>
+      </c>
       <c r="C347" s="1" t="n">
         <v>45454</v>
       </c>
@@ -22267,7 +23651,11 @@
       <c r="A348" t="n">
         <v>116</v>
       </c>
-      <c r="B348" t="inlineStr"/>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Puits_45</t>
+        </is>
+      </c>
       <c r="C348" s="1" t="n">
         <v>45454</v>
       </c>
@@ -22332,7 +23720,11 @@
       <c r="A349" t="n">
         <v>116</v>
       </c>
-      <c r="B349" t="inlineStr"/>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Puits_45</t>
+        </is>
+      </c>
       <c r="C349" s="1" t="n">
         <v>45454</v>
       </c>
@@ -22397,7 +23789,11 @@
       <c r="A350" t="n">
         <v>117</v>
       </c>
-      <c r="B350" t="inlineStr"/>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Puits_14</t>
+        </is>
+      </c>
       <c r="C350" s="1" t="n">
         <v>45455</v>
       </c>
@@ -22462,7 +23858,11 @@
       <c r="A351" t="n">
         <v>117</v>
       </c>
-      <c r="B351" t="inlineStr"/>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Puits_14</t>
+        </is>
+      </c>
       <c r="C351" s="1" t="n">
         <v>45455</v>
       </c>
@@ -22527,7 +23927,11 @@
       <c r="A352" t="n">
         <v>117</v>
       </c>
-      <c r="B352" t="inlineStr"/>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Puits_14</t>
+        </is>
+      </c>
       <c r="C352" s="1" t="n">
         <v>45455</v>
       </c>
@@ -22592,7 +23996,11 @@
       <c r="A353" t="n">
         <v>118</v>
       </c>
-      <c r="B353" t="inlineStr"/>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Puits_162</t>
+        </is>
+      </c>
       <c r="C353" s="1" t="n">
         <v>45456</v>
       </c>
@@ -22657,7 +24065,11 @@
       <c r="A354" t="n">
         <v>118</v>
       </c>
-      <c r="B354" t="inlineStr"/>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Puits_162</t>
+        </is>
+      </c>
       <c r="C354" s="1" t="n">
         <v>45456</v>
       </c>
@@ -22722,7 +24134,11 @@
       <c r="A355" t="n">
         <v>118</v>
       </c>
-      <c r="B355" t="inlineStr"/>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Puits_162</t>
+        </is>
+      </c>
       <c r="C355" s="1" t="n">
         <v>45456</v>
       </c>
@@ -22787,7 +24203,11 @@
       <c r="A356" t="n">
         <v>119</v>
       </c>
-      <c r="B356" t="inlineStr"/>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Puits_84</t>
+        </is>
+      </c>
       <c r="C356" s="1" t="n">
         <v>45457</v>
       </c>
@@ -22850,7 +24270,11 @@
       <c r="A357" t="n">
         <v>119</v>
       </c>
-      <c r="B357" t="inlineStr"/>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Puits_84</t>
+        </is>
+      </c>
       <c r="C357" s="1" t="n">
         <v>45457</v>
       </c>
@@ -22915,7 +24339,11 @@
       <c r="A358" t="n">
         <v>119</v>
       </c>
-      <c r="B358" t="inlineStr"/>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Puits_84</t>
+        </is>
+      </c>
       <c r="C358" s="1" t="n">
         <v>45457</v>
       </c>
@@ -22980,7 +24408,11 @@
       <c r="A359" t="n">
         <v>120</v>
       </c>
-      <c r="B359" t="inlineStr"/>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Puits_20</t>
+        </is>
+      </c>
       <c r="C359" s="1" t="n">
         <v>45458</v>
       </c>
@@ -23045,7 +24477,11 @@
       <c r="A360" t="n">
         <v>120</v>
       </c>
-      <c r="B360" t="inlineStr"/>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Puits_20</t>
+        </is>
+      </c>
       <c r="C360" s="1" t="n">
         <v>45458</v>
       </c>
@@ -23110,7 +24546,11 @@
       <c r="A361" t="n">
         <v>120</v>
       </c>
-      <c r="B361" t="inlineStr"/>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Puits_20</t>
+        </is>
+      </c>
       <c r="C361" s="1" t="n">
         <v>45458</v>
       </c>
@@ -23175,7 +24615,11 @@
       <c r="A362" t="n">
         <v>121</v>
       </c>
-      <c r="B362" t="inlineStr"/>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Puits_12</t>
+        </is>
+      </c>
       <c r="C362" s="1" t="n">
         <v>45461</v>
       </c>
@@ -23240,7 +24684,11 @@
       <c r="A363" t="n">
         <v>121</v>
       </c>
-      <c r="B363" t="inlineStr"/>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Puits_12</t>
+        </is>
+      </c>
       <c r="C363" s="1" t="n">
         <v>45461</v>
       </c>
@@ -23305,7 +24753,11 @@
       <c r="A364" t="n">
         <v>121</v>
       </c>
-      <c r="B364" t="inlineStr"/>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Puits_12</t>
+        </is>
+      </c>
       <c r="C364" s="1" t="n">
         <v>45461</v>
       </c>
@@ -23370,7 +24822,11 @@
       <c r="A365" t="n">
         <v>122</v>
       </c>
-      <c r="B365" t="inlineStr"/>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Puits_209</t>
+        </is>
+      </c>
       <c r="C365" s="1" t="n">
         <v>45462</v>
       </c>
@@ -23433,7 +24889,11 @@
       <c r="A366" t="n">
         <v>122</v>
       </c>
-      <c r="B366" t="inlineStr"/>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Puits_209</t>
+        </is>
+      </c>
       <c r="C366" s="1" t="n">
         <v>45462</v>
       </c>
@@ -23496,7 +24956,11 @@
       <c r="A367" t="n">
         <v>122</v>
       </c>
-      <c r="B367" t="inlineStr"/>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>Puits_209</t>
+        </is>
+      </c>
       <c r="C367" s="1" t="n">
         <v>45462</v>
       </c>
@@ -23559,7 +25023,11 @@
       <c r="A368" t="n">
         <v>123</v>
       </c>
-      <c r="B368" t="inlineStr"/>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>Puits_219</t>
+        </is>
+      </c>
       <c r="C368" s="1" t="n">
         <v>45463</v>
       </c>
@@ -23622,7 +25090,11 @@
       <c r="A369" t="n">
         <v>123</v>
       </c>
-      <c r="B369" t="inlineStr"/>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>Puits_219</t>
+        </is>
+      </c>
       <c r="C369" s="1" t="n">
         <v>45463</v>
       </c>
@@ -23685,7 +25157,11 @@
       <c r="A370" t="n">
         <v>123</v>
       </c>
-      <c r="B370" t="inlineStr"/>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>Puits_219</t>
+        </is>
+      </c>
       <c r="C370" s="1" t="n">
         <v>45463</v>
       </c>
@@ -23748,7 +25224,11 @@
       <c r="A371" t="n">
         <v>124</v>
       </c>
-      <c r="B371" t="inlineStr"/>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>Puits_195</t>
+        </is>
+      </c>
       <c r="C371" s="1" t="n">
         <v>45464</v>
       </c>
@@ -23811,7 +25291,11 @@
       <c r="A372" t="n">
         <v>124</v>
       </c>
-      <c r="B372" t="inlineStr"/>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>Puits_195</t>
+        </is>
+      </c>
       <c r="C372" s="1" t="n">
         <v>45464</v>
       </c>
@@ -23874,7 +25358,11 @@
       <c r="A373" t="n">
         <v>124</v>
       </c>
-      <c r="B373" t="inlineStr"/>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>Puits_195</t>
+        </is>
+      </c>
       <c r="C373" s="1" t="n">
         <v>45464</v>
       </c>
@@ -23937,7 +25425,11 @@
       <c r="A374" t="n">
         <v>125</v>
       </c>
-      <c r="B374" t="inlineStr"/>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>Puits_154</t>
+        </is>
+      </c>
       <c r="C374" s="1" t="n">
         <v>45465</v>
       </c>
@@ -24000,7 +25492,11 @@
       <c r="A375" t="n">
         <v>125</v>
       </c>
-      <c r="B375" t="inlineStr"/>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>Puits_154</t>
+        </is>
+      </c>
       <c r="C375" s="1" t="n">
         <v>45465</v>
       </c>
@@ -24063,7 +25559,11 @@
       <c r="A376" t="n">
         <v>125</v>
       </c>
-      <c r="B376" t="inlineStr"/>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>Puits_154</t>
+        </is>
+      </c>
       <c r="C376" s="1" t="n">
         <v>45465</v>
       </c>
@@ -24126,7 +25626,11 @@
       <c r="A377" t="n">
         <v>126</v>
       </c>
-      <c r="B377" t="inlineStr"/>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>Puits_259</t>
+        </is>
+      </c>
       <c r="C377" s="1" t="n">
         <v>45466</v>
       </c>
@@ -24189,7 +25693,11 @@
       <c r="A378" t="n">
         <v>126</v>
       </c>
-      <c r="B378" t="inlineStr"/>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>Puits_259</t>
+        </is>
+      </c>
       <c r="C378" s="1" t="n">
         <v>45466</v>
       </c>
@@ -24252,7 +25760,11 @@
       <c r="A379" t="n">
         <v>126</v>
       </c>
-      <c r="B379" t="inlineStr"/>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>Puits_259</t>
+        </is>
+      </c>
       <c r="C379" s="1" t="n">
         <v>45466</v>
       </c>
@@ -24315,7 +25827,11 @@
       <c r="A380" t="n">
         <v>127</v>
       </c>
-      <c r="B380" t="inlineStr"/>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>Puits_175</t>
+        </is>
+      </c>
       <c r="C380" s="1" t="n">
         <v>45467</v>
       </c>
@@ -24378,7 +25894,11 @@
       <c r="A381" t="n">
         <v>127</v>
       </c>
-      <c r="B381" t="inlineStr"/>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>Puits_175</t>
+        </is>
+      </c>
       <c r="C381" s="1" t="n">
         <v>45467</v>
       </c>
@@ -24441,7 +25961,11 @@
       <c r="A382" t="n">
         <v>127</v>
       </c>
-      <c r="B382" t="inlineStr"/>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>Puits_175</t>
+        </is>
+      </c>
       <c r="C382" s="1" t="n">
         <v>45467</v>
       </c>
@@ -24504,7 +26028,11 @@
       <c r="A383" t="n">
         <v>128</v>
       </c>
-      <c r="B383" t="inlineStr"/>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>Puits_37</t>
+        </is>
+      </c>
       <c r="C383" s="1" t="n">
         <v>45468</v>
       </c>
@@ -24567,7 +26095,11 @@
       <c r="A384" t="n">
         <v>128</v>
       </c>
-      <c r="B384" t="inlineStr"/>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>Puits_37</t>
+        </is>
+      </c>
       <c r="C384" s="1" t="n">
         <v>45468</v>
       </c>
@@ -24630,7 +26162,11 @@
       <c r="A385" t="n">
         <v>128</v>
       </c>
-      <c r="B385" t="inlineStr"/>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>Puits_37</t>
+        </is>
+      </c>
       <c r="C385" s="1" t="n">
         <v>45468</v>
       </c>
@@ -24693,7 +26229,11 @@
       <c r="A386" t="n">
         <v>129</v>
       </c>
-      <c r="B386" t="inlineStr"/>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>Puits_41</t>
+        </is>
+      </c>
       <c r="C386" s="1" t="n">
         <v>45474</v>
       </c>
@@ -24756,7 +26296,11 @@
       <c r="A387" t="n">
         <v>129</v>
       </c>
-      <c r="B387" t="inlineStr"/>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>Puits_41</t>
+        </is>
+      </c>
       <c r="C387" s="1" t="n">
         <v>45474</v>
       </c>
@@ -24819,7 +26363,11 @@
       <c r="A388" t="n">
         <v>129</v>
       </c>
-      <c r="B388" t="inlineStr"/>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>Puits_41</t>
+        </is>
+      </c>
       <c r="C388" s="1" t="n">
         <v>45474</v>
       </c>
@@ -24882,7 +26430,11 @@
       <c r="A389" t="n">
         <v>130</v>
       </c>
-      <c r="B389" t="inlineStr"/>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>Puits_19</t>
+        </is>
+      </c>
       <c r="C389" s="1" t="n">
         <v>45475</v>
       </c>
@@ -24945,7 +26497,11 @@
       <c r="A390" t="n">
         <v>130</v>
       </c>
-      <c r="B390" t="inlineStr"/>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>Puits_19</t>
+        </is>
+      </c>
       <c r="C390" s="1" t="n">
         <v>45475</v>
       </c>
@@ -25008,7 +26564,11 @@
       <c r="A391" t="n">
         <v>130</v>
       </c>
-      <c r="B391" t="inlineStr"/>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>Puits_19</t>
+        </is>
+      </c>
       <c r="C391" t="inlineStr"/>
       <c r="D391" t="inlineStr"/>
       <c r="E391" t="inlineStr"/>
@@ -25035,7 +26595,11 @@
       <c r="A392" t="n">
         <v>131</v>
       </c>
-      <c r="B392" t="inlineStr"/>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Puits_33</t>
+        </is>
+      </c>
       <c r="C392" s="1" t="n">
         <v>45477</v>
       </c>
@@ -25098,7 +26662,11 @@
       <c r="A393" t="n">
         <v>131</v>
       </c>
-      <c r="B393" t="inlineStr"/>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>Puits_33</t>
+        </is>
+      </c>
       <c r="C393" s="1" t="n">
         <v>45477</v>
       </c>
@@ -25161,7 +26729,11 @@
       <c r="A394" t="n">
         <v>131</v>
       </c>
-      <c r="B394" t="inlineStr"/>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>Puits_33</t>
+        </is>
+      </c>
       <c r="C394" s="1" t="n">
         <v>45477</v>
       </c>
@@ -25224,7 +26796,11 @@
       <c r="A395" t="n">
         <v>132</v>
       </c>
-      <c r="B395" t="inlineStr"/>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>Puits_121</t>
+        </is>
+      </c>
       <c r="C395" s="1" t="n">
         <v>45478</v>
       </c>
@@ -25287,7 +26863,11 @@
       <c r="A396" t="n">
         <v>132</v>
       </c>
-      <c r="B396" t="inlineStr"/>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>Puits_121</t>
+        </is>
+      </c>
       <c r="C396" s="1" t="n">
         <v>45478</v>
       </c>
@@ -25350,7 +26930,11 @@
       <c r="A397" t="n">
         <v>132</v>
       </c>
-      <c r="B397" t="inlineStr"/>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>Puits_121</t>
+        </is>
+      </c>
       <c r="C397" s="1" t="n">
         <v>45478</v>
       </c>
@@ -25413,7 +26997,11 @@
       <c r="A398" t="n">
         <v>133</v>
       </c>
-      <c r="B398" t="inlineStr"/>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Puits_7</t>
+        </is>
+      </c>
       <c r="C398" s="1" t="n">
         <v>45479</v>
       </c>
@@ -25476,7 +27064,11 @@
       <c r="A399" t="n">
         <v>133</v>
       </c>
-      <c r="B399" t="inlineStr"/>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Puits_7</t>
+        </is>
+      </c>
       <c r="C399" s="1" t="n">
         <v>45479</v>
       </c>
@@ -25539,7 +27131,11 @@
       <c r="A400" t="n">
         <v>133</v>
       </c>
-      <c r="B400" t="inlineStr"/>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Puits_7</t>
+        </is>
+      </c>
       <c r="C400" s="1" t="n">
         <v>45479</v>
       </c>
@@ -25602,7 +27198,11 @@
       <c r="A401" t="n">
         <v>134</v>
       </c>
-      <c r="B401" t="inlineStr"/>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Puits_260</t>
+        </is>
+      </c>
       <c r="C401" s="1" t="n">
         <v>45480</v>
       </c>
@@ -25665,7 +27265,11 @@
       <c r="A402" t="n">
         <v>134</v>
       </c>
-      <c r="B402" t="inlineStr"/>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>Puits_260</t>
+        </is>
+      </c>
       <c r="C402" s="1" t="n">
         <v>45480</v>
       </c>
@@ -25728,7 +27332,11 @@
       <c r="A403" t="n">
         <v>134</v>
       </c>
-      <c r="B403" t="inlineStr"/>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Puits_260</t>
+        </is>
+      </c>
       <c r="C403" s="1" t="n">
         <v>45480</v>
       </c>
@@ -25968,7 +27576,11 @@
       <c r="A407" t="n">
         <v>136</v>
       </c>
-      <c r="B407" t="inlineStr"/>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>Puits_67</t>
+        </is>
+      </c>
       <c r="C407" s="1" t="n">
         <v>45578</v>
       </c>
@@ -26029,7 +27641,11 @@
       <c r="A408" t="n">
         <v>136</v>
       </c>
-      <c r="B408" t="inlineStr"/>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>Puits_67</t>
+        </is>
+      </c>
       <c r="C408" s="1" t="n">
         <v>45578</v>
       </c>
@@ -26090,7 +27706,11 @@
       <c r="A409" t="n">
         <v>136</v>
       </c>
-      <c r="B409" t="inlineStr"/>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>Puits_67</t>
+        </is>
+      </c>
       <c r="C409" s="1" t="n">
         <v>45578</v>
       </c>
@@ -26151,7 +27771,11 @@
       <c r="A410" t="n">
         <v>137</v>
       </c>
-      <c r="B410" t="inlineStr"/>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>Puits_77</t>
+        </is>
+      </c>
       <c r="C410" s="1" t="n">
         <v>45575</v>
       </c>
@@ -26212,7 +27836,11 @@
       <c r="A411" t="n">
         <v>137</v>
       </c>
-      <c r="B411" t="inlineStr"/>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>Puits_77</t>
+        </is>
+      </c>
       <c r="C411" s="1" t="n">
         <v>45575</v>
       </c>
@@ -26273,7 +27901,11 @@
       <c r="A412" t="n">
         <v>137</v>
       </c>
-      <c r="B412" t="inlineStr"/>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>Puits_77</t>
+        </is>
+      </c>
       <c r="C412" s="1" t="n">
         <v>45575</v>
       </c>
@@ -26334,7 +27966,11 @@
       <c r="A413" t="n">
         <v>138</v>
       </c>
-      <c r="B413" t="inlineStr"/>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>Puits_107</t>
+        </is>
+      </c>
       <c r="C413" s="1" t="n">
         <v>45587</v>
       </c>
@@ -26397,7 +28033,11 @@
       <c r="A414" t="n">
         <v>138</v>
       </c>
-      <c r="B414" t="inlineStr"/>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>Puits_107</t>
+        </is>
+      </c>
       <c r="C414" s="1" t="n">
         <v>45588</v>
       </c>
@@ -26460,7 +28100,11 @@
       <c r="A415" t="n">
         <v>138</v>
       </c>
-      <c r="B415" t="inlineStr"/>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Puits_107</t>
+        </is>
+      </c>
       <c r="C415" s="1" t="n">
         <v>45588</v>
       </c>
@@ -26523,7 +28167,11 @@
       <c r="A416" t="n">
         <v>139</v>
       </c>
-      <c r="B416" t="inlineStr"/>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Puits_128</t>
+        </is>
+      </c>
       <c r="C416" s="1" t="n">
         <v>45581</v>
       </c>
@@ -26586,7 +28234,11 @@
       <c r="A417" t="n">
         <v>139</v>
       </c>
-      <c r="B417" t="inlineStr"/>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Puits_128</t>
+        </is>
+      </c>
       <c r="C417" s="1" t="n">
         <v>45581</v>
       </c>
@@ -26649,7 +28301,11 @@
       <c r="A418" t="n">
         <v>139</v>
       </c>
-      <c r="B418" t="inlineStr"/>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>Puits_128</t>
+        </is>
+      </c>
       <c r="C418" s="1" t="n">
         <v>45581</v>
       </c>
